--- a/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
+++ b/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
@@ -477,16 +477,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2450775236234141</v>
+        <v>0.2383251469878226</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.004339404329904339</v>
+        <v>0.004166810025328339</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>11477.623051125</v>
+        <v>11750.01481470833</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.002687074258367496</v>
+        <v>0.002750845031536803</v>
       </c>
     </row>
     <row r="3">
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1750970206979293</v>
+        <v>0.1684205155328952</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.008659340580795587</v>
+        <v>0.008024904176163462</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>16461.713024862</v>
+        <v>15702.92379319009</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.00495927716111289</v>
+        <v>0.004730683326373721</v>
       </c>
     </row>
     <row r="4">
@@ -515,16 +515,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2117038386324727</v>
+        <v>0.2188801373808927</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.01683486623128776</v>
+        <v>0.01744485572097463</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>27909.0398997235</v>
+        <v>28361.52023238683</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.00882687581816813</v>
+        <v>0.00896998313110089</v>
       </c>
     </row>
     <row r="5">
@@ -534,16 +534,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.33179036970737</v>
+        <v>0.3091594452478542</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.04476058384763521</v>
+        <v>0.04416542793877021</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>58909.05337304167</v>
+        <v>57770.89926825</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.02849027035251038</v>
+        <v>0.02793982324308232</v>
       </c>
     </row>
     <row r="6">
@@ -553,16 +553,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2115353034643711</v>
+        <v>0.2033405280009292</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.0444398523346281</v>
+        <v>0.04661312905935756</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>45050.61178104141</v>
+        <v>43971.97323549975</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.01599645039894638</v>
+        <v>0.01561345031726025</v>
       </c>
     </row>
     <row r="7">
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.2620713526958388</v>
+        <v>0.2752174806000208</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.03579417696456377</v>
+        <v>0.03790414060347432</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>42691.30968896208</v>
+        <v>43906.01368217049</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.01891007634429468</v>
+        <v>0.01944812836037583</v>
       </c>
     </row>
     <row r="8">
@@ -591,16 +591,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.114210567338352</v>
+        <v>0.0809190666850048</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.00326779591793031</v>
+        <v>0.003067888711316467</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>14123.29376908333</v>
+        <v>14355.70722483333</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.003193116871405832</v>
+        <v>0.003245662923256825</v>
       </c>
     </row>
     <row r="9">
@@ -610,16 +610,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.274223651759406</v>
+        <v>0.2795209940422606</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.004051827461604602</v>
+        <v>0.004126479108205109</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>15327.04152175</v>
+        <v>15959.80240673875</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.002938136656828398</v>
+        <v>0.003059434556919189</v>
       </c>
     </row>
     <row r="10">
@@ -629,16 +629,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.2899507651266203</v>
+        <v>0.2771352070694275</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.01241951491837849</v>
+        <v>0.012120122833664</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>22085.99445614158</v>
+        <v>22188.84958908333</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.005768955011509425</v>
+        <v>0.005795821206546378</v>
       </c>
     </row>
     <row r="11">
@@ -648,16 +648,16 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.1661393848908191</v>
+        <v>0.160589770556958</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.01176105462639742</v>
+        <v>0.01192879837713902</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>33055.07580742909</v>
+        <v>33552.57813172825</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.007680143606954755</v>
+        <v>0.007795735212845207</v>
       </c>
     </row>
     <row r="12">
@@ -667,16 +667,16 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.1404172678841986</v>
+        <v>0.1516479181323103</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.004564295653874169</v>
+        <v>0.005143899761958984</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>12213.5308173095</v>
+        <v>13321.20409847617</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.003073717288315769</v>
+        <v>0.003352479798932453</v>
       </c>
     </row>
     <row r="13">
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.1403718958716038</v>
+        <v>0.1539424190142067</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.001806437411562599</v>
+        <v>0.001677051162684811</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>6852.046973333336</v>
+        <v>6169.757047125002</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.001566741232321869</v>
+        <v>0.001410733580309463</v>
       </c>
     </row>
     <row r="14">
@@ -705,16 +705,16 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.3056608067577107</v>
+        <v>0.2905381406077925</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.006500891331082437</v>
+        <v>0.006891415249000402</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>16221.66285370109</v>
+        <v>16786.23574868917</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.0042040814070812</v>
+        <v>0.004350398737934855</v>
       </c>
     </row>
     <row r="15">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.1602896331149101</v>
+        <v>0.1765381358936561</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.01654057580705324</v>
+        <v>0.01825834970900518</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>22941.824598</v>
+        <v>25578.15599762501</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.007337272228358126</v>
+        <v>0.008180425791867776</v>
       </c>
     </row>
     <row r="16">
@@ -743,16 +743,16 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.1961382473728854</v>
+        <v>0.185829288101121</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.08805707485509216</v>
+        <v>0.08020964916381002</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>60883.73540276534</v>
+        <v>58318.54421191984</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.02692563573693484</v>
+        <v>0.02579118820109651</v>
       </c>
     </row>
     <row r="17">
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.2029193466082301</v>
+        <v>0.2104106499910562</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.1019307753346457</v>
+        <v>0.0976452578074902</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>75550.85665408635</v>
+        <v>75547.19546053867</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.03939862056646436</v>
+        <v>0.03939671130981535</v>
       </c>
     </row>
     <row r="18">
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.1957328233694937</v>
+        <v>0.2103540306409665</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.06868798936166957</v>
+        <v>0.07634007490347565</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>86183.06465065094</v>
+        <v>86507.43874374585</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.05224031811576766</v>
+        <v>0.05243693917908771</v>
       </c>
     </row>
     <row r="19">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.1991947856165345</v>
+        <v>0.1802928946918994</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.03628171765130457</v>
+        <v>0.03689532038113075</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>51173.04832484484</v>
+        <v>47333.72386479159</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.01927178188608727</v>
+        <v>0.01782589140259729</v>
       </c>
     </row>
     <row r="20">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.1363466212651061</v>
+        <v>0.09199478395980647</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.007708445160197927</v>
+        <v>0.00769692505654863</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>20155.77036841667</v>
+        <v>20058.76196508333</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.004316600375831348</v>
+        <v>0.004295824860798511</v>
       </c>
     </row>
     <row r="21">
@@ -838,16 +838,16 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.2371725106664641</v>
+        <v>0.2435161632081426</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.0161395960247424</v>
+        <v>0.01532090467130832</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>23709.46384304167</v>
+        <v>24231.81794279167</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.005502387826458567</v>
+        <v>0.005623613462710508</v>
       </c>
     </row>
     <row r="22">
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.180504601038479</v>
+        <v>0.1733874799128063</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.02142255635987605</v>
+        <v>0.02018431522576355</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>32429.68328308334</v>
+        <v>31499.37420145834</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.007953154711569502</v>
+        <v>0.007725002867126379</v>
       </c>
     </row>
     <row r="23">
@@ -876,16 +876,16 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.1488975455325735</v>
+        <v>0.1582473477086962</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.02298022881713996</v>
+        <v>0.02078583787110265</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>43133.53627858333</v>
+        <v>40401.63756257066</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.01029601973605536</v>
+        <v>0.009643912686095334</v>
       </c>
     </row>
     <row r="24">
@@ -895,16 +895,16 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.1205502667287155</v>
+        <v>0.125278917779533</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.01950930041156958</v>
+        <v>0.01968785895006485</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>19372.60437107509</v>
+        <v>19645.93764339034</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.005350209020355227</v>
+        <v>0.005425696554766849</v>
       </c>
     </row>
     <row r="25">
@@ -914,16 +914,16 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.134791943570057</v>
+        <v>0.1338466614517063</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.003073829901785221</v>
+        <v>0.002126334539312187</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4709.652537916669</v>
+        <v>4303.196366000001</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.001110490273774102</v>
+        <v>0.001014651860643825</v>
       </c>
     </row>
     <row r="26">
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.09552186913324143</v>
+        <v>0.07742101700972326</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.02274738111940062</v>
+        <v>0.01877505038995717</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>22381.74417120834</v>
+        <v>21130.68222679167</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.00612243241828648</v>
+        <v>0.005780209660882512</v>
       </c>
     </row>
     <row r="27">
@@ -952,16 +952,16 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.08174023072032199</v>
+        <v>0.1019481114329708</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.03102070112214012</v>
+        <v>0.03493319601260502</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>35884.26919194543</v>
+        <v>38650.83884688018</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.0141219975005328</v>
+        <v>0.01521076120206048</v>
       </c>
     </row>
     <row r="28">
@@ -971,16 +971,16 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.1478399595607992</v>
+        <v>0.1348284296169824</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.07661332602003347</v>
+        <v>0.06721871597288599</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>62558.61714961719</v>
+        <v>60263.2810881786</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.02676055475035679</v>
+        <v>0.0257786841601599</v>
       </c>
     </row>
     <row r="29">
@@ -990,16 +990,16 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.2130429795513027</v>
+        <v>0.2342474171997666</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.1524723826462124</v>
+        <v>0.1481093835858429</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>94998.94745142493</v>
+        <v>91765.8978407086</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.05052076017899827</v>
+        <v>0.04880141350820152</v>
       </c>
     </row>
     <row r="30">
@@ -1009,16 +1009,16 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.1986261742111359</v>
+        <v>0.2125626447219825</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>0.111119025852807</v>
+        <v>0.1134755295194264</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>76631.99532008242</v>
+        <v>76153.09102810734</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.03904157021141584</v>
+        <v>0.03879758366948127</v>
       </c>
     </row>
     <row r="31">
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.1960037857077285</v>
+        <v>0.1984632435991037</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.05575168010388165</v>
+        <v>0.06450435871498218</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>61039.71301522617</v>
+        <v>61165.1234906845</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.02656787257644821</v>
+        <v>0.02662245817928185</v>
       </c>
     </row>
     <row r="32">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.2454826716710426</v>
+        <v>0.2445047855762782</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.04112145200834343</v>
+        <v>0.04164278404849855</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>49875.3300984645</v>
+        <v>49942.22299615384</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.01835834061357343</v>
+        <v>0.01838296285863898</v>
       </c>
     </row>
     <row r="33">
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.1804133260099773</v>
+        <v>0.1901459136112586</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.01573269101256879</v>
+        <v>0.01634192154475747</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>38502.33401466667</v>
+        <v>38256.19778633333</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.009664590855464315</v>
+        <v>0.009602807433694542</v>
       </c>
     </row>
     <row r="34">
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.1838549120540531</v>
+        <v>0.1884474917470045</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.02435351398009794</v>
+        <v>0.02551756926786939</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>51106.95832232726</v>
+        <v>52263.15856598317</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.01209308821964795</v>
+        <v>0.01236667193515545</v>
       </c>
     </row>
     <row r="35">
@@ -1104,16 +1104,16 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.1596134438976789</v>
+        <v>0.1614185027861602</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.03590157965829174</v>
+        <v>0.03166251240761631</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>53242.99638755943</v>
+        <v>51785.55609966668</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.0147357285678446</v>
+        <v>0.01433236200428945</v>
       </c>
     </row>
     <row r="36">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.1335779410600143</v>
+        <v>0.1505582459694361</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>-0.007841703623868561</v>
+        <v>-0.008462234911870252</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>5377.428862166669</v>
+        <v>5726.312655583335</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.00145141543599877</v>
+        <v>0.001545582246218687</v>
       </c>
     </row>
     <row r="37">
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.1263288259762004</v>
+        <v>0.1422513083133574</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>-0.009979263644046511</v>
+        <v>-0.009354088632910885</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5253.238523458336</v>
+        <v>5754.774981375002</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.001250634576205299</v>
+        <v>0.001370034986580191</v>
       </c>
     </row>
   </sheetData>
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2130535946549281</v>
+        <v>0.2075149730726323</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.008477333675767855</v>
+        <v>0.008452891051833358</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.006956013264846315</v>
+        <v>0.006975437200226719</v>
       </c>
     </row>
     <row r="3">
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1811133170088835</v>
+        <v>0.1781925799779407</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.01703918150560598</v>
+        <v>0.01665755688624512</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.01124952893790349</v>
+        <v>0.01109542729084748</v>
       </c>
     </row>
     <row r="4">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.1617900535820845</v>
+        <v>0.1673064489825816</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.02891233549021781</v>
+        <v>0.02866530337198913</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.01500123564853095</v>
+        <v>0.01489357456009723</v>
       </c>
     </row>
     <row r="5">
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.1801855927879046</v>
+        <v>0.1802821814701738</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.01365972456010923</v>
+        <v>0.01352159753050007</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.01084113179262575</v>
+        <v>0.01076394500185774</v>
       </c>
     </row>
   </sheetData>

--- a/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
+++ b/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Carbon Emission" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Monthly Analysis'!$A$1:$E$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Annual Summary'!$A$1:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Monthly Analysis'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Annual Summary'!$A$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly Carbon Emission'!$A$1:$B$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,14 +433,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -456,15 +457,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>profit_increment_k20</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>cost reduction</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>carbon reduction</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>rate carbon</t>
         </is>
@@ -480,12 +486,15 @@
         <v>0.2383251469878226</v>
       </c>
       <c r="C2" s="2" t="n">
+        <v>1.191625734939113</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>0.004166810025328339</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>11750.01481470833</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="F2" s="2" t="n">
         <v>0.002750845031536803</v>
       </c>
     </row>
@@ -499,12 +508,15 @@
         <v>0.1684205155328952</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>0.8421025776644759</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>0.008024904176163462</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>15702.92379319009</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>0.004730683326373721</v>
       </c>
     </row>
@@ -518,12 +530,15 @@
         <v>0.2188801373808927</v>
       </c>
       <c r="C4" s="2" t="n">
+        <v>1.094400686904464</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>0.01744485572097463</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>28361.52023238683</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>0.00896998313110089</v>
       </c>
     </row>
@@ -537,12 +552,15 @@
         <v>0.3091594452478542</v>
       </c>
       <c r="C5" s="2" t="n">
+        <v>1.545797226239271</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>0.04416542793877021</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>57770.89926825</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>0.02793982324308232</v>
       </c>
     </row>
@@ -556,12 +574,15 @@
         <v>0.2033405280009292</v>
       </c>
       <c r="C6" s="2" t="n">
+        <v>1.016702640004646</v>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>0.04661312905935756</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>43971.97323549975</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>0.01561345031726025</v>
       </c>
     </row>
@@ -575,12 +596,15 @@
         <v>0.2752174806000208</v>
       </c>
       <c r="C7" s="2" t="n">
+        <v>1.376087403000104</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>0.03790414060347432</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>43906.01368217049</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>0.01944812836037583</v>
       </c>
     </row>
@@ -594,12 +618,15 @@
         <v>0.0809190666850048</v>
       </c>
       <c r="C8" s="2" t="n">
+        <v>0.404595333425024</v>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>0.003067888711316467</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>14355.70722483333</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>0.003245662923256825</v>
       </c>
     </row>
@@ -613,12 +640,15 @@
         <v>0.2795209940422606</v>
       </c>
       <c r="C9" s="2" t="n">
+        <v>1.397604970211303</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.004126479108205109</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>15959.80240673875</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>0.003059434556919189</v>
       </c>
     </row>
@@ -632,12 +662,15 @@
         <v>0.2771352070694275</v>
       </c>
       <c r="C10" s="2" t="n">
+        <v>1.385676035347137</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>0.012120122833664</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>22188.84958908333</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>0.005795821206546378</v>
       </c>
     </row>
@@ -651,12 +684,15 @@
         <v>0.160589770556958</v>
       </c>
       <c r="C11" s="2" t="n">
+        <v>0.8029488527847899</v>
+      </c>
+      <c r="D11" s="2" t="n">
         <v>0.01192879837713902</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>33552.57813172825</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>0.007795735212845207</v>
       </c>
     </row>
@@ -670,12 +706,15 @@
         <v>0.1516479181323103</v>
       </c>
       <c r="C12" s="2" t="n">
+        <v>0.7582395906615514</v>
+      </c>
+      <c r="D12" s="2" t="n">
         <v>0.005143899761958984</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>13321.20409847617</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>0.003352479798932453</v>
       </c>
     </row>
@@ -689,12 +728,15 @@
         <v>0.1539424190142067</v>
       </c>
       <c r="C13" s="2" t="n">
+        <v>0.7697120950710333</v>
+      </c>
+      <c r="D13" s="2" t="n">
         <v>0.001677051162684811</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>6169.757047125002</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>0.001410733580309463</v>
       </c>
     </row>
@@ -708,12 +750,15 @@
         <v>0.2905381406077925</v>
       </c>
       <c r="C14" s="2" t="n">
+        <v>1.452690703038962</v>
+      </c>
+      <c r="D14" s="2" t="n">
         <v>0.006891415249000402</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>16786.23574868917</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>0.004350398737934855</v>
       </c>
     </row>
@@ -727,12 +772,15 @@
         <v>0.1765381358936561</v>
       </c>
       <c r="C15" s="2" t="n">
+        <v>0.8826906794682804</v>
+      </c>
+      <c r="D15" s="2" t="n">
         <v>0.01825834970900518</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>25578.15599762501</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="F15" s="2" t="n">
         <v>0.008180425791867776</v>
       </c>
     </row>
@@ -746,12 +794,15 @@
         <v>0.185829288101121</v>
       </c>
       <c r="C16" s="2" t="n">
+        <v>0.929146440505605</v>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>0.08020964916381002</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>58318.54421191984</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="F16" s="2" t="n">
         <v>0.02579118820109651</v>
       </c>
     </row>
@@ -765,12 +816,15 @@
         <v>0.2104106499910562</v>
       </c>
       <c r="C17" s="2" t="n">
+        <v>1.052053249955281</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>0.0976452578074902</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>75547.19546053867</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" s="2" t="n">
         <v>0.03939671130981535</v>
       </c>
     </row>
@@ -784,12 +838,15 @@
         <v>0.2103540306409665</v>
       </c>
       <c r="C18" s="2" t="n">
+        <v>1.051770153204833</v>
+      </c>
+      <c r="D18" s="2" t="n">
         <v>0.07634007490347565</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>86507.43874374585</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="F18" s="2" t="n">
         <v>0.05243693917908771</v>
       </c>
     </row>
@@ -803,12 +860,15 @@
         <v>0.1802928946918994</v>
       </c>
       <c r="C19" s="2" t="n">
+        <v>0.9014644734594968</v>
+      </c>
+      <c r="D19" s="2" t="n">
         <v>0.03689532038113075</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>47333.72386479159</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="F19" s="2" t="n">
         <v>0.01782589140259729</v>
       </c>
     </row>
@@ -822,12 +882,15 @@
         <v>0.09199478395980647</v>
       </c>
       <c r="C20" s="2" t="n">
+        <v>0.4599739197990323</v>
+      </c>
+      <c r="D20" s="2" t="n">
         <v>0.00769692505654863</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>20058.76196508333</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="F20" s="2" t="n">
         <v>0.004295824860798511</v>
       </c>
     </row>
@@ -841,12 +904,15 @@
         <v>0.2435161632081426</v>
       </c>
       <c r="C21" s="2" t="n">
+        <v>1.217580816040713</v>
+      </c>
+      <c r="D21" s="2" t="n">
         <v>0.01532090467130832</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>24231.81794279167</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="F21" s="2" t="n">
         <v>0.005623613462710508</v>
       </c>
     </row>
@@ -860,12 +926,15 @@
         <v>0.1733874799128063</v>
       </c>
       <c r="C22" s="2" t="n">
+        <v>0.8669373995640316</v>
+      </c>
+      <c r="D22" s="2" t="n">
         <v>0.02018431522576355</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>31499.37420145834</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="F22" s="2" t="n">
         <v>0.007725002867126379</v>
       </c>
     </row>
@@ -879,12 +948,15 @@
         <v>0.1582473477086962</v>
       </c>
       <c r="C23" s="2" t="n">
+        <v>0.7912367385434812</v>
+      </c>
+      <c r="D23" s="2" t="n">
         <v>0.02078583787110265</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>40401.63756257066</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="F23" s="2" t="n">
         <v>0.009643912686095334</v>
       </c>
     </row>
@@ -898,12 +970,15 @@
         <v>0.125278917779533</v>
       </c>
       <c r="C24" s="2" t="n">
+        <v>0.6263945888976649</v>
+      </c>
+      <c r="D24" s="2" t="n">
         <v>0.01968785895006485</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>19645.93764339034</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>0.005425696554766849</v>
       </c>
     </row>
@@ -917,12 +992,15 @@
         <v>0.1338466614517063</v>
       </c>
       <c r="C25" s="2" t="n">
+        <v>0.6692333072585314</v>
+      </c>
+      <c r="D25" s="2" t="n">
         <v>0.002126334539312187</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>4303.196366000001</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="F25" s="2" t="n">
         <v>0.001014651860643825</v>
       </c>
     </row>
@@ -936,12 +1014,15 @@
         <v>0.07742101700972326</v>
       </c>
       <c r="C26" s="2" t="n">
+        <v>0.3871050850486163</v>
+      </c>
+      <c r="D26" s="2" t="n">
         <v>0.01877505038995717</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>21130.68222679167</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="F26" s="2" t="n">
         <v>0.005780209660882512</v>
       </c>
     </row>
@@ -955,12 +1036,15 @@
         <v>0.1019481114329708</v>
       </c>
       <c r="C27" s="2" t="n">
+        <v>0.5097405571648538</v>
+      </c>
+      <c r="D27" s="2" t="n">
         <v>0.03493319601260502</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>38650.83884688018</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="F27" s="2" t="n">
         <v>0.01521076120206048</v>
       </c>
     </row>
@@ -974,12 +1058,15 @@
         <v>0.1348284296169824</v>
       </c>
       <c r="C28" s="2" t="n">
+        <v>0.6741421480849118</v>
+      </c>
+      <c r="D28" s="2" t="n">
         <v>0.06721871597288599</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>60263.2810881786</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="F28" s="2" t="n">
         <v>0.0257786841601599</v>
       </c>
     </row>
@@ -993,12 +1080,15 @@
         <v>0.2342474171997666</v>
       </c>
       <c r="C29" s="2" t="n">
+        <v>1.171237085998833</v>
+      </c>
+      <c r="D29" s="2" t="n">
         <v>0.1481093835858429</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>91765.8978407086</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="F29" s="2" t="n">
         <v>0.04880141350820152</v>
       </c>
     </row>
@@ -1012,12 +1102,15 @@
         <v>0.2125626447219825</v>
       </c>
       <c r="C30" s="2" t="n">
+        <v>1.062813223609912</v>
+      </c>
+      <c r="D30" s="2" t="n">
         <v>0.1134755295194264</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>76153.09102810734</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="F30" s="2" t="n">
         <v>0.03879758366948127</v>
       </c>
     </row>
@@ -1031,12 +1124,15 @@
         <v>0.1984632435991037</v>
       </c>
       <c r="C31" s="2" t="n">
+        <v>0.9923162179955184</v>
+      </c>
+      <c r="D31" s="2" t="n">
         <v>0.06450435871498218</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>61165.1234906845</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="F31" s="2" t="n">
         <v>0.02662245817928185</v>
       </c>
     </row>
@@ -1050,12 +1146,15 @@
         <v>0.2445047855762782</v>
       </c>
       <c r="C32" s="2" t="n">
+        <v>1.222523927881391</v>
+      </c>
+      <c r="D32" s="2" t="n">
         <v>0.04164278404849855</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>49942.22299615384</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="F32" s="2" t="n">
         <v>0.01838296285863898</v>
       </c>
     </row>
@@ -1069,12 +1168,15 @@
         <v>0.1901459136112586</v>
       </c>
       <c r="C33" s="2" t="n">
+        <v>0.9507295680562928</v>
+      </c>
+      <c r="D33" s="2" t="n">
         <v>0.01634192154475747</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>38256.19778633333</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="F33" s="2" t="n">
         <v>0.009602807433694542</v>
       </c>
     </row>
@@ -1088,12 +1190,15 @@
         <v>0.1884474917470045</v>
       </c>
       <c r="C34" s="2" t="n">
+        <v>0.9422374587350225</v>
+      </c>
+      <c r="D34" s="2" t="n">
         <v>0.02551756926786939</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>52263.15856598317</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="F34" s="2" t="n">
         <v>0.01236667193515545</v>
       </c>
     </row>
@@ -1107,12 +1212,15 @@
         <v>0.1614185027861602</v>
       </c>
       <c r="C35" s="2" t="n">
+        <v>0.8070925139308008</v>
+      </c>
+      <c r="D35" s="2" t="n">
         <v>0.03166251240761631</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>51785.55609966668</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="F35" s="2" t="n">
         <v>0.01433236200428945</v>
       </c>
     </row>
@@ -1126,12 +1234,15 @@
         <v>0.1505582459694361</v>
       </c>
       <c r="C36" s="2" t="n">
+        <v>0.7527912298471805</v>
+      </c>
+      <c r="D36" s="2" t="n">
         <v>-0.008462234911870252</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>5726.312655583335</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="F36" s="2" t="n">
         <v>0.001545582246218687</v>
       </c>
     </row>
@@ -1145,17 +1256,20 @@
         <v>0.1422513083133574</v>
       </c>
       <c r="C37" s="2" t="n">
+        <v>0.7112565415667871</v>
+      </c>
+      <c r="D37" s="2" t="n">
         <v>-0.009354088632910885</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>5754.774981375002</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="F37" s="2" t="n">
         <v>0.001370034986580191</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E37"/>
+  <autoFilter ref="A1:F37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1166,13 +1280,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1188,10 +1303,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>profit_increment_rate_k20</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>cost reduction rate</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>carbon reduction rate</t>
         </is>
@@ -1207,9 +1327,12 @@
         <v>0.2075149730726323</v>
       </c>
       <c r="C2" s="2" t="n">
+        <v>1.037574865363161</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>0.008452891051833358</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="n">
         <v>0.006975437200226719</v>
       </c>
     </row>
@@ -1223,9 +1346,12 @@
         <v>0.1781925799779407</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>0.8909628998897036</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>0.01665755688624512</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>0.01109542729084748</v>
       </c>
     </row>
@@ -1239,9 +1365,12 @@
         <v>0.1673064489825816</v>
       </c>
       <c r="C4" s="2" t="n">
+        <v>0.836532244912908</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>0.02866530337198913</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E4" s="2" t="n">
         <v>0.01489357456009723</v>
       </c>
     </row>
@@ -1255,14 +1384,17 @@
         <v>0.1802821814701738</v>
       </c>
       <c r="C5" s="2" t="n">
+        <v>0.9014109073508689</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>0.01352159753050007</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="E5" s="2" t="n">
         <v>0.01076394500185774</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D5"/>
+  <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
+++ b/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2383251469878226</v>
+        <v>0.2383251471938371</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.191625734939113</v>
+        <v>1.191625735969186</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.004166810025328339</v>
+        <v>0.004166810026604245</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>11750.01481470833</v>
@@ -505,19 +505,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1684205155328952</v>
+        <v>0.1684205150053425</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.8421025776644759</v>
+        <v>0.8421025750267123</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.008024904176163462</v>
+        <v>0.00802490419140622</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>15702.92379319009</v>
+        <v>15702.92383838033</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.004730683326373721</v>
+        <v>0.004730683339987794</v>
       </c>
     </row>
     <row r="4">
@@ -527,13 +527,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2188801373808927</v>
+        <v>0.2188801377080097</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.094400686904464</v>
+        <v>1.094400688540049</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.01744485572097463</v>
+        <v>0.0174448557381771</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>28361.52023238683</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.3091594452478542</v>
+        <v>0.3091594452391085</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.545797226239271</v>
+        <v>1.545797226195543</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.04416542793877021</v>
+        <v>0.04416542794173372</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>57770.89926825</v>
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2033405280009292</v>
+        <v>0.2033405280900995</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.016702640004646</v>
+        <v>1.016702640450498</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.04661312905935756</v>
+        <v>0.04661312909978984</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>43971.97323549975</v>
+        <v>43971.97328069</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.01561345031726025</v>
+        <v>0.01561345033330629</v>
       </c>
     </row>
     <row r="7">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.0809190666850048</v>
+        <v>0.08091906664130973</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.404595333425024</v>
+        <v>0.4045953332065486</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.003067888711316467</v>
+        <v>0.003067888711583154</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>14355.70722483333</v>
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.2795209940422606</v>
+        <v>0.279520994072654</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1.397604970211303</v>
+        <v>1.39760497036327</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.004126479108205109</v>
+        <v>0.004126479109571591</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>15959.80240673875</v>
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.2771352070694275</v>
+        <v>0.2771352071343227</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.385676035347137</v>
+        <v>1.385676035671613</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.012120122833664</v>
+        <v>0.01212012281687765</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>22188.84958908333</v>
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.160589770556958</v>
+        <v>0.1605897700758065</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.8029488527847899</v>
+        <v>0.8029488503790327</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.01192879837713902</v>
+        <v>0.01192879835449084</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>33552.57813172825</v>
+        <v>33552.57808653801</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.007795735212845207</v>
+        <v>0.007795735202345533</v>
       </c>
     </row>
     <row r="12">
@@ -703,13 +703,13 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.1516479181323103</v>
+        <v>0.1516479184851465</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.7582395906615514</v>
+        <v>0.7582395924257326</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.005143899761958984</v>
+        <v>0.005143899796979566</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>13321.20409847617</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.1539424190142067</v>
+        <v>0.1539424204326353</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.7697120950710333</v>
+        <v>0.7697121021631766</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.001677051162684811</v>
+        <v>0.001677051179389759</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>6169.757047125002</v>
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.2905381406077925</v>
+        <v>0.2905381420481664</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1.452690703038962</v>
+        <v>1.452690710240832</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.006891415249000402</v>
+        <v>0.006891415204709482</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>16786.23574868917</v>
+        <v>16786.23570349892</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.004350398737934855</v>
+        <v>0.00435039872622314</v>
       </c>
     </row>
     <row r="15">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.1765381358936561</v>
+        <v>0.1765381359405996</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.8826906794682804</v>
+        <v>0.8826906797029979</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.01825834970900518</v>
+        <v>0.01825834970671907</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>25578.15599762501</v>
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.185829288101121</v>
+        <v>0.1858292881094196</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.929146440505605</v>
+        <v>0.9291464405470983</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.08020964916381002</v>
+        <v>0.08020964908465314</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>58318.54421191984</v>
@@ -813,19 +813,19 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.2104106499910562</v>
+        <v>0.2104654123203737</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1.052053249955281</v>
+        <v>1.052327061601869</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.0976452578074902</v>
+        <v>0.09777600162892791</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>75547.19546053867</v>
+        <v>76653.95925779727</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.03939671130981535</v>
+        <v>0.03997387176617574</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.2103540306409665</v>
+        <v>0.210362032955713</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1.051770153204833</v>
+        <v>1.051810164778565</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.07634007490347565</v>
+        <v>0.07629083904968723</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>86507.43874374585</v>
+        <v>86671.63030174426</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.05243693917908771</v>
+        <v>0.05253646475591107</v>
       </c>
     </row>
     <row r="19">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.1802928946918994</v>
+        <v>0.1794918116253356</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.9014644734594968</v>
+        <v>0.8974590581266779</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.03689532038113075</v>
+        <v>0.03689076359783989</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>47333.72386479159</v>
+        <v>47545.02018785808</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.01782589140259729</v>
+        <v>0.017905465646946</v>
       </c>
     </row>
     <row r="20">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.09199478395980647</v>
+        <v>0.09199478413827572</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.4599739197990323</v>
+        <v>0.4599739206913787</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.00769692505654863</v>
+        <v>0.007696925039565091</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>20058.76196508333</v>
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.2435161632081426</v>
+        <v>0.2435161637796327</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1.217580816040713</v>
+        <v>1.217580818898164</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.01532090467130832</v>
+        <v>0.01532090465644187</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>24231.81794279167</v>
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.1733874799128063</v>
+        <v>0.1733874800037439</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.8669373995640316</v>
+        <v>0.8669374000187198</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.02018431522576355</v>
+        <v>0.02018431524582334</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>31499.37420145834</v>
@@ -945,13 +945,13 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.1582473477086962</v>
+        <v>0.1582473477589069</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.7912367385434812</v>
+        <v>0.7912367387945343</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.02078583787110265</v>
+        <v>0.02078583786744845</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>40401.63756257066</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.125278917779533</v>
+        <v>0.1252789177313883</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.6263945888976649</v>
+        <v>0.6263945886569416</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.01968785895006485</v>
+        <v>0.01968785890026978</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>19645.93764339034</v>
@@ -989,13 +989,13 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.1338466614517063</v>
+        <v>0.1338466615231491</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.6692333072585314</v>
+        <v>0.6692333076157454</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.002126334539312187</v>
+        <v>0.002126334554229525</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>4303.196366000001</v>
@@ -1011,13 +1011,13 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.07742101700972326</v>
+        <v>0.07742101701177029</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.3871050850486163</v>
+        <v>0.3871050850588514</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.01877505038995717</v>
+        <v>0.01877505042843148</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>21130.68222679167</v>
@@ -1033,19 +1033,19 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.1019481114329708</v>
+        <v>0.1019481115667868</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.5097405571648538</v>
+        <v>0.5097405578339341</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.03493319601260502</v>
+        <v>0.03493319611853878</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>38650.83884688018</v>
+        <v>38650.83898245093</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.01521076120206048</v>
+        <v>0.01521076125541338</v>
       </c>
     </row>
     <row r="28">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.1348284296169824</v>
+        <v>0.1348266243575372</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.6741421480849118</v>
+        <v>0.6741331217876861</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.06721871597288599</v>
+        <v>0.06721721330530633</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>60263.2810881786</v>
+        <v>60263.28113336885</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.0257786841601599</v>
+        <v>0.02577868417949083</v>
       </c>
     </row>
     <row r="29">
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.2342474171997666</v>
+        <v>0.2342631359734838</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1.171237085998833</v>
+        <v>1.171315679867419</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.1481093835858429</v>
+        <v>0.1480107242884021</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>91765.8978407086</v>
+        <v>92132.18319432694</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.04880141350820152</v>
+        <v>0.04899620529278096</v>
       </c>
     </row>
     <row r="30">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.2125626447219825</v>
+        <v>0.212562644820658</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1.062813223609912</v>
+        <v>1.06281322410329</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.1134755295194264</v>
+        <v>0.1134755296305709</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>76153.09102810734</v>
+        <v>76153.09116367808</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.03879758366948127</v>
+        <v>0.03879758373855026</v>
       </c>
     </row>
     <row r="31">
@@ -1121,13 +1121,13 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.1984632435991037</v>
+        <v>0.1984632438527574</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.9923162179955184</v>
+        <v>0.992316219263787</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.06450435871498218</v>
+        <v>0.06450435840330637</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>61165.1234906845</v>
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.2445047855762782</v>
+        <v>0.2445047855898335</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1.222523927881391</v>
+        <v>1.222523927949168</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.04164278404849855</v>
+        <v>0.04164278415334666</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>49942.22299615384</v>
+        <v>49942.22313172458</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.01838296285863898</v>
+        <v>0.01838296290854048</v>
       </c>
     </row>
     <row r="33">
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.1901459136112586</v>
+        <v>0.1901459136283381</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.9507295680562928</v>
+        <v>0.9507295681416907</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.01634192154475747</v>
+        <v>0.016341921547367</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>38256.19778633333</v>
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.1884474917470045</v>
+        <v>0.1884474918518809</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.9422374587350225</v>
+        <v>0.9422374592594046</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.02551756926786939</v>
+        <v>0.02551756924426026</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>52263.15856598317</v>
+        <v>52263.15852079292</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.01236667193515545</v>
+        <v>0.01236667192446239</v>
       </c>
     </row>
     <row r="35">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.1614185027861602</v>
+        <v>0.161418502797649</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.8070925139308008</v>
+        <v>0.807092513988245</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.03166251240761631</v>
+        <v>0.03166251240959781</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>51785.55609966668</v>
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.1422513083133574</v>
+        <v>0.1422513083400622</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.7112565415667871</v>
+        <v>0.7112565417003111</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>-0.009354088632910885</v>
+        <v>-0.009354088753895758</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>5754.774981375002</v>
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2075149730726323</v>
+        <v>0.2075149731619904</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.037574865363161</v>
+        <v>1.037574865809952</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.008452891051833358</v>
+        <v>0.008452891056693319</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.006975437200226719</v>
+        <v>0.006975437201253462</v>
       </c>
     </row>
     <row r="3">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1781925799779407</v>
+        <v>0.1781378227449829</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.8909628998897036</v>
+        <v>0.8906891137249144</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.01665755688624512</v>
+        <v>0.01665881505864658</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.01109542729084748</v>
+        <v>0.0111319572245281</v>
       </c>
     </row>
     <row r="4">
@@ -1362,16 +1362,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.1673064489825816</v>
+        <v>0.1673081245746617</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.836532244912908</v>
+        <v>0.8365406228733083</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.02866530337198913</v>
+        <v>0.02866287279878727</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.01489357456009723</v>
+        <v>0.01490344203563604</v>
       </c>
     </row>
     <row r="5">
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.1802821814701738</v>
+        <v>0.1802642706276622</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.9014109073508689</v>
+        <v>0.9013213531383109</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.01352159753050007</v>
+        <v>0.0135214748277375</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.01076394500185774</v>
+        <v>0.01077913304322589</v>
       </c>
     </row>
   </sheetData>

--- a/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
+++ b/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
@@ -439,7 +439,7 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2383251471938371</v>
+        <v>0.2997203031524047</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.191625735969186</v>
+        <v>1.498601515762024</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.004166810026604245</v>
+        <v>0.005168931257677989</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>11750.01481470833</v>
+        <v>13230.94449745833</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.002750845031536803</v>
+        <v>0.003097551663323235</v>
       </c>
     </row>
     <row r="3">
@@ -505,19 +505,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1684205150053425</v>
+        <v>0.2256718289794861</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.8421025750267123</v>
+        <v>1.128359144897431</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.00802490419140622</v>
+        <v>0.009504939324228715</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>15702.92383838033</v>
+        <v>17734.94104298175</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.004730683339987794</v>
+        <v>0.005342851496397066</v>
       </c>
     </row>
     <row r="4">
@@ -527,19 +527,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2188801377080097</v>
+        <v>0.2757832222055511</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.094400688540049</v>
+        <v>1.378916111027755</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.0174448557381771</v>
+        <v>0.02003801573768792</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>28361.52023238683</v>
+        <v>31278.16631592275</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.00896998313110089</v>
+        <v>0.009892439542264394</v>
       </c>
     </row>
     <row r="5">
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.3091594452391085</v>
+        <v>0.3816287679204478</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.545797226195543</v>
+        <v>1.908143839602239</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.04416542794173372</v>
+        <v>0.04839144964169494</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>57770.89926825</v>
+        <v>62438.65096952759</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.02793982324308232</v>
+        <v>0.03019729472315616</v>
       </c>
     </row>
     <row r="6">
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2033405280900995</v>
+        <v>0.3036859796250664</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.016702640450498</v>
+        <v>1.518429898125332</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.04661312909978984</v>
+        <v>0.05439610966217928</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>43971.97328069</v>
+        <v>49219.50200099741</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.01561345033330629</v>
+        <v>0.01747672875668098</v>
       </c>
     </row>
     <row r="7">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.2752174806000208</v>
+        <v>0.3532127870294353</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1.376087403000104</v>
+        <v>1.766063935147177</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.03790414060347432</v>
+        <v>0.04283804944682859</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>43906.01368217049</v>
+        <v>48077.96249875383</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.01944812836037583</v>
+        <v>0.02129608924986052</v>
       </c>
     </row>
     <row r="8">
@@ -615,19 +615,19 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.08091906664130973</v>
+        <v>0.1767100630301979</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.4045953332065486</v>
+        <v>0.8835503151509894</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.003067888711583154</v>
+        <v>0.003623869839263565</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>14355.70722483333</v>
+        <v>15696.381435</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.003245662923256825</v>
+        <v>0.003548774188202192</v>
       </c>
     </row>
     <row r="9">
@@ -637,19 +637,19 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.279520994072654</v>
+        <v>0.3435212975154837</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1.39760497036327</v>
+        <v>1.717606487577418</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.004126479109571591</v>
+        <v>0.005028867983812313</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>15959.80240673875</v>
+        <v>18002.35609471308</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.003059434556919189</v>
+        <v>0.003450984475777386</v>
       </c>
     </row>
     <row r="10">
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.2771352071343227</v>
+        <v>0.3681046925539374</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.385676035671613</v>
+        <v>1.840523462769687</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.01212012281687765</v>
+        <v>0.01475917471994923</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>22188.84958908333</v>
+        <v>25137.12601569691</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.005795821206546378</v>
+        <v>0.006565923458469106</v>
       </c>
     </row>
     <row r="11">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.1605897700758065</v>
+        <v>0.21968712708478</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.8029488503790327</v>
+        <v>1.0984356354239</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.01192879835449084</v>
+        <v>0.01290955717619189</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>33552.57808653801</v>
+        <v>35731.51490963659</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.007795735202345533</v>
+        <v>0.008301997774828207</v>
       </c>
     </row>
     <row r="12">
@@ -703,19 +703,19 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.1516479184851465</v>
+        <v>0.1993136678741139</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.7582395924257326</v>
+        <v>0.9965683393705693</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.005143899796979566</v>
+        <v>0.0063671404549787</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>13321.20409847617</v>
+        <v>15968.94603622617</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.003352479798932453</v>
+        <v>0.004018823568870527</v>
       </c>
     </row>
     <row r="13">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.1539424204326353</v>
+        <v>0.2085685845319942</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.7697121021631766</v>
+        <v>1.042842922659971</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.001677051179389759</v>
+        <v>0.002628373231021836</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>6169.757047125002</v>
+        <v>7295.242818500002</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.001410733580309463</v>
+        <v>0.001668079300685776</v>
       </c>
     </row>
     <row r="14">
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.2905381420481664</v>
+        <v>0.4176476025635765</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1.452690710240832</v>
+        <v>2.088238012817883</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.006891415204709482</v>
+        <v>0.008874127422099091</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>16786.23570349892</v>
+        <v>18879.63218857742</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.00435039872622314</v>
+        <v>0.004892933071804098</v>
       </c>
     </row>
     <row r="15">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.1765381359405996</v>
+        <v>0.2224710200193104</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.8826906797029979</v>
+        <v>1.112355100096552</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.01825834970671907</v>
+        <v>0.0223117309902379</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>25578.15599762501</v>
+        <v>28128.67864420834</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.008180425791867776</v>
+        <v>0.008996135933083212</v>
       </c>
     </row>
     <row r="16">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.1858292881094196</v>
+        <v>0.2408651905154017</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.9291464405470983</v>
+        <v>1.204325952577008</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.08020964908465314</v>
+        <v>0.0986278146627588</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>58318.54421191984</v>
+        <v>65147.67597771243</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.02579118820109651</v>
+        <v>0.02881134971235802</v>
       </c>
     </row>
     <row r="17">
@@ -813,19 +813,19 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.2104654123203737</v>
+        <v>0.2632066347027275</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1.052327061601869</v>
+        <v>1.316033173513637</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.09777600162892791</v>
+        <v>0.1200236601911251</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>76653.95925779727</v>
+        <v>79257.49853327077</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.03997387176617574</v>
+        <v>0.04133157782785439</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.210362032955713</v>
+        <v>0.2672496204801186</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1.051810164778565</v>
+        <v>1.336248102400593</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.07629083904968723</v>
+        <v>0.1104431591460852</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>86671.63030174426</v>
+        <v>91940.81667531542</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.05253646475591107</v>
+        <v>0.05573040980163934</v>
       </c>
     </row>
     <row r="19">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.1794918116253356</v>
+        <v>0.2443169171490906</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0.8974590581266779</v>
+        <v>1.221584585745453</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.03689076359783989</v>
+        <v>0.05318485217936716</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>47545.02018785808</v>
+        <v>54021.87887642058</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.017905465646946</v>
+        <v>0.02034465213356349</v>
       </c>
     </row>
     <row r="20">
@@ -879,19 +879,19 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.09199478413827572</v>
+        <v>0.1776869363325705</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.4599739206913787</v>
+        <v>0.8884346816628528</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.007696925039565091</v>
+        <v>0.01109980216394766</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>20058.76196508333</v>
+        <v>22976.09387091667</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.004295824860798511</v>
+        <v>0.004920606537259642</v>
       </c>
     </row>
     <row r="21">
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.2435161637796327</v>
+        <v>0.312200981953635</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1.217580818898164</v>
+        <v>1.561004909768175</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.01532090465644187</v>
+        <v>0.02225309449570587</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>24231.81794279167</v>
+        <v>26422.68645304166</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.005623613462710508</v>
+        <v>0.00613206056636397</v>
       </c>
     </row>
     <row r="22">
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.1733874800037439</v>
+        <v>0.2364537194924721</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.8669374000187198</v>
+        <v>1.182268597462361</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.02018431524582334</v>
+        <v>0.02708866063360133</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>31499.37420145834</v>
+        <v>35977.80329354167</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.007725002867126379</v>
+        <v>0.008823306514535483</v>
       </c>
     </row>
     <row r="23">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.1582473477589069</v>
+        <v>0.2317398304912713</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.7912367387945343</v>
+        <v>1.158699152456357</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.02078583786744845</v>
+        <v>0.02803704449169174</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>40401.63756257066</v>
+        <v>47953.47788113751</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.009643912686095334</v>
+        <v>0.01144654478334142</v>
       </c>
     </row>
     <row r="24">
@@ -967,19 +967,19 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.1252789177313883</v>
+        <v>0.1721761989041884</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.6263945886569416</v>
+        <v>0.8608809945209422</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.01968785890026978</v>
+        <v>0.02741132126892678</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>19645.93764339034</v>
+        <v>23505.73866433334</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.005425696554766849</v>
+        <v>0.006491673118550851</v>
       </c>
     </row>
     <row r="25">
@@ -989,19 +989,19 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.1338466615231491</v>
+        <v>0.1828738984561135</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.6692333076157454</v>
+        <v>0.9143694922805677</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.002126334554229525</v>
+        <v>0.005399982475536585</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>4303.196366000001</v>
+        <v>4961.076025500001</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.001014651860643825</v>
+        <v>0.001169773487410741</v>
       </c>
     </row>
     <row r="26">
@@ -1011,19 +1011,19 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.07742101701177029</v>
+        <v>0.1473881771126137</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.3871050850588514</v>
+        <v>0.7369408855630686</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.01877505042843148</v>
+        <v>0.02785476964453</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>21130.68222679167</v>
+        <v>24850.71953545184</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.005780209660882512</v>
+        <v>0.006797810292967059</v>
       </c>
     </row>
     <row r="27">
@@ -1033,19 +1033,19 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.1019481115667868</v>
+        <v>0.1335741832675398</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.5097405578339341</v>
+        <v>0.6678709163376991</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.03493319611853878</v>
+        <v>0.04194970664046396</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>38650.83898245093</v>
+        <v>41351.9238226961</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.01521076125541338</v>
+        <v>0.01627375387645947</v>
       </c>
     </row>
     <row r="28">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.1348266243575372</v>
+        <v>0.200445728873049</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.6741331217876861</v>
+        <v>1.002228644365245</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.06721721330530633</v>
+        <v>0.09654389320401623</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>60263.28113336885</v>
+        <v>67930.49684490827</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.02577868417949083</v>
+        <v>0.02905847128445086</v>
       </c>
     </row>
     <row r="29">
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.2342631359734838</v>
+        <v>0.3000077252085593</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1.171315679867419</v>
+        <v>1.500038626042797</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.1480107242884021</v>
+        <v>0.183864225114019</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>92132.18319432694</v>
+        <v>100400.0771837554</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.04899620529278096</v>
+        <v>0.05339309915983015</v>
       </c>
     </row>
     <row r="30">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.212562644820658</v>
+        <v>0.2555159253650321</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1.06281322410329</v>
+        <v>1.277579626825161</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.1134755296305709</v>
+        <v>0.1394747224462796</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>76153.09116367808</v>
+        <v>82958.27768549827</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.03879758373855026</v>
+        <v>0.04226461035430898</v>
       </c>
     </row>
     <row r="31">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.1984632438527574</v>
+        <v>0.2417199043547115</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.992316219263787</v>
+        <v>1.208599521773557</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.06450435840330637</v>
+        <v>0.08759928236310492</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>61165.1234906845</v>
+        <v>65401.73881691042</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.02662245817928185</v>
+        <v>0.02846646842412885</v>
       </c>
     </row>
     <row r="32">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.2445047855898335</v>
+        <v>0.3084101360387435</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1.222523927949168</v>
+        <v>1.542050680193717</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.04164278415334666</v>
+        <v>0.05517166215190767</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>49942.22313172458</v>
+        <v>54346.91297311675</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.01838296290854048</v>
+        <v>0.02000426137906255</v>
       </c>
     </row>
     <row r="33">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.1901459136283381</v>
+        <v>0.2700442971692155</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.9507295681416907</v>
+        <v>1.350221485846078</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.016341921547367</v>
+        <v>0.02195112932523458</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>38256.19778633333</v>
+        <v>43086.57672485191</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.009602807433694542</v>
+        <v>0.01081529590516879</v>
       </c>
     </row>
     <row r="34">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.1884474918518809</v>
+        <v>0.2470992362514883</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.9422374592594046</v>
+        <v>1.235496181257441</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.02551756924426026</v>
+        <v>0.0313393487851536</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>52263.15852079292</v>
+        <v>56610.06355938326</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.01236667192446239</v>
+        <v>0.01339525018150845</v>
       </c>
     </row>
     <row r="35">
@@ -1209,19 +1209,19 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.161418502797649</v>
+        <v>0.2199483814758137</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.807092513988245</v>
+        <v>1.099741907379068</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.03166251240959781</v>
+        <v>0.04851319129978881</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>51785.55609966668</v>
+        <v>61235.00307225001</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.01433236200428945</v>
+        <v>0.01694762589159322</v>
       </c>
     </row>
     <row r="36">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.1505582459694361</v>
+        <v>0.2029909949064889</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.7527912298471805</v>
+        <v>1.014954974532444</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-0.008462234911870252</v>
+        <v>-0.001524668424752511</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>5726.312655583335</v>
+        <v>7364.248330250002</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.001545582246218687</v>
+        <v>0.001987675518360346</v>
       </c>
     </row>
     <row r="37">
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.1422513083400622</v>
+        <v>0.1821814767902196</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.7112565417003111</v>
+        <v>0.910907383951098</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>-0.009354088753895758</v>
+        <v>-0.004767203097243841</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>5754.774981375002</v>
+        <v>6342.187977708337</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.001370034986580191</v>
+        <v>0.001509879960389451</v>
       </c>
     </row>
   </sheetData>
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2075149731619904</v>
+        <v>0.2762573303438485</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.037574865809952</v>
+        <v>1.381286651719243</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.008452891056693319</v>
+        <v>0.009862392972247181</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.006975437201253462</v>
+        <v>0.007720679502288893</v>
       </c>
     </row>
     <row r="3">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.1781378227449829</v>
+        <v>0.24200964424526</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.8906891137249144</v>
+        <v>1.2100482212263</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.01665881505864658</v>
+        <v>0.02254217765269077</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.0111319572245281</v>
+        <v>0.01230206684399515</v>
       </c>
     </row>
     <row r="4">
@@ -1362,16 +1362,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.1673081245746617</v>
+        <v>0.2232856160072505</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.8365406228733083</v>
+        <v>1.116428080036252</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.02866287279878727</v>
+        <v>0.03954967126742035</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.01490344203563604</v>
+        <v>0.01648356034242582</v>
       </c>
     </row>
     <row r="5">
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.1802642706276622</v>
+        <v>0.241871177504544</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.9013213531383109</v>
+        <v>1.20935588752272</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.0135214748277375</v>
+        <v>0.01744355049129132</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.01077913304322589</v>
+        <v>0.01192064984990754</v>
       </c>
     </row>
   </sheetData>

--- a/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
+++ b/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
@@ -505,19 +505,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.2256718289794861</v>
+        <v>0.227697995930277</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.128359144897431</v>
+        <v>1.138489979651385</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.009504939324228715</v>
+        <v>0.009883412598133585</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>17734.94104298175</v>
+        <v>17621.6257228725</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.005342851496397066</v>
+        <v>0.005308713975096989</v>
       </c>
     </row>
     <row r="4">
@@ -527,19 +527,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2757832222055511</v>
+        <v>0.2758927295067184</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.378916111027755</v>
+        <v>1.379463647533592</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.02003801573768792</v>
+        <v>0.01998801386816578</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>31278.16631592275</v>
+        <v>31259.00852703533</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.009892439542264394</v>
+        <v>0.009886380450870799</v>
       </c>
     </row>
     <row r="5">
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.3816287679204478</v>
+        <v>0.3813217175427082</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.908143839602239</v>
+        <v>1.906608587713541</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.04839144964169494</v>
+        <v>0.04819778871982623</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>62438.65096952759</v>
+        <v>62397.20397856925</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.03019729472315616</v>
+        <v>0.03017724965520669</v>
       </c>
     </row>
     <row r="6">
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.3036859796250664</v>
+        <v>0.3036777259695075</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.518429898125332</v>
+        <v>1.518388629847538</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.05439610966217928</v>
+        <v>0.0533249176301254</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>49219.50200099741</v>
+        <v>49277.66149122542</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.01747672875668098</v>
+        <v>0.01749737987247896</v>
       </c>
     </row>
     <row r="7">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.3532127870294353</v>
+        <v>0.3526902062099536</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1.766063935147177</v>
+        <v>1.763451031049768</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.04283804944682859</v>
+        <v>0.04272188407356232</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>48077.96249875383</v>
+        <v>47892.37840362501</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.02129608924986052</v>
+        <v>0.02121388494568851</v>
       </c>
     </row>
     <row r="8">
@@ -615,19 +615,19 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.1767100630301979</v>
+        <v>0.1770574448165846</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.8835503151509894</v>
+        <v>0.8852872240829228</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.003623869839263565</v>
+        <v>0.003906979036475333</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>15696.381435</v>
+        <v>15819.995748655</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.003548774188202192</v>
+        <v>0.003576721985432261</v>
       </c>
     </row>
     <row r="9">
@@ -637,19 +637,19 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.3435212975154837</v>
+        <v>0.3431448157787283</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1.717606487577418</v>
+        <v>1.715724078893642</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.005028867983812313</v>
+        <v>0.005033554592624196</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>18002.35609471308</v>
+        <v>17814.36560370833</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.003450984475777386</v>
+        <v>0.003414947400261382</v>
       </c>
     </row>
     <row r="10">
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.3681046925539374</v>
+        <v>0.3673031120633016</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.840523462769687</v>
+        <v>1.836515560316508</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.01475917471994923</v>
+        <v>0.01495614367621184</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>25137.12601569691</v>
+        <v>25267.96890148825</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.006565923458469106</v>
+        <v>0.006600100172730499</v>
       </c>
     </row>
     <row r="11">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.21968712708478</v>
+        <v>0.2209584831305381</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1.0984356354239</v>
+        <v>1.104792415652691</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.01290955717619189</v>
+        <v>0.01326562505672426</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>35731.51490963659</v>
+        <v>36153.68492148817</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.008301997774828207</v>
+        <v>0.008400086381142677</v>
       </c>
     </row>
     <row r="12">
@@ -703,19 +703,19 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.1993136678741139</v>
+        <v>0.1992975838182589</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.9965683393705693</v>
+        <v>0.9964879190912946</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.0063671404549787</v>
+        <v>0.006337750218607837</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>15968.94603622617</v>
+        <v>15936.5783690295</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.004018823568870527</v>
+        <v>0.004010677762409398</v>
       </c>
     </row>
     <row r="13">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.2085685845319942</v>
+        <v>0.2075551359136039</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1.042842922659971</v>
+        <v>1.03777567956802</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.002628373231021836</v>
+        <v>0.002761549537777851</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7295.242818500002</v>
+        <v>7465.91886104167</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.001668079300685776</v>
+        <v>0.00170710489322188</v>
       </c>
     </row>
     <row r="14">
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.4176476025635765</v>
+        <v>0.416862015320279</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2.088238012817883</v>
+        <v>2.084310076601395</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.008874127422099091</v>
+        <v>0.008850101150716114</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>18879.63218857742</v>
+        <v>18875.12474734484</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.004892933071804098</v>
+        <v>0.004891764902421569</v>
       </c>
     </row>
     <row r="15">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.2224710200193104</v>
+        <v>0.2229038768359136</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.112355100096552</v>
+        <v>1.114519384179568</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.0223117309902379</v>
+        <v>0.02227431473470587</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>28128.67864420834</v>
+        <v>28087.55551670834</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.008996135933083212</v>
+        <v>0.00898298390238661</v>
       </c>
     </row>
     <row r="16">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.2408651905154017</v>
+        <v>0.2406992030632521</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1.204325952577008</v>
+        <v>1.20349601531626</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.0986278146627588</v>
+        <v>0.09870638990650184</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>65147.67597771243</v>
+        <v>65055.26629991668</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.02881134971235802</v>
+        <v>0.02877048183021453</v>
       </c>
     </row>
     <row r="17">
@@ -813,19 +813,19 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.2632066347027275</v>
+        <v>0.2630533589445115</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1.316033173513637</v>
+        <v>1.315266794722558</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.1200236601911251</v>
+        <v>0.1201133840188465</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>79257.49853327077</v>
+        <v>78890.81363758877</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.04133157782785439</v>
+        <v>0.04114035724198368</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.2672496204801186</v>
+        <v>0.2672783238260033</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1.336248102400593</v>
+        <v>1.336391619130016</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.1104431591460852</v>
+        <v>0.1125483579082448</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>91940.81667531542</v>
+        <v>92041.12714527968</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.05573040980163934</v>
+        <v>0.05579121352082148</v>
       </c>
     </row>
     <row r="19">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.2443169171490906</v>
+        <v>0.2445197893704994</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1.221584585745453</v>
+        <v>1.222598946852497</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.05318485217936716</v>
+        <v>0.05329477027163858</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>54021.87887642058</v>
+        <v>53822.08270374483</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.02034465213356349</v>
+        <v>0.0202694088485233</v>
       </c>
     </row>
     <row r="20">
@@ -879,19 +879,19 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.1776869363325705</v>
+        <v>0.1781779437415121</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.8884346816628528</v>
+        <v>0.8908897187075603</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.01109980216394766</v>
+        <v>0.01108254495932466</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>22976.09387091667</v>
+        <v>22877.97830645834</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.004920606537259642</v>
+        <v>0.004899593910370451</v>
       </c>
     </row>
     <row r="21">
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.312200981953635</v>
+        <v>0.3126772377182015</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1.561004909768175</v>
+        <v>1.563386188591007</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.02225309449570587</v>
+        <v>0.02219170999381749</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>26422.68645304166</v>
+        <v>26232.25888198125</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.00613206056636397</v>
+        <v>0.006087866975325326</v>
       </c>
     </row>
     <row r="22">
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.2364537194924721</v>
+        <v>0.2361198048629374</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1.182268597462361</v>
+        <v>1.180599024314687</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.02708866063360133</v>
+        <v>0.02711344606662317</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>35977.80329354167</v>
+        <v>36187.03415104167</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.008823306514535483</v>
+        <v>0.008874618929942261</v>
       </c>
     </row>
     <row r="23">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.2317398304912713</v>
+        <v>0.2314311704253437</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1.158699152456357</v>
+        <v>1.157155852126719</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.02803704449169174</v>
+        <v>0.02806627729492727</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>47953.47788113751</v>
+        <v>47470.820071934</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.01144654478334142</v>
+        <v>0.01133133386492229</v>
       </c>
     </row>
     <row r="24">
@@ -967,19 +967,19 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.1721761989041884</v>
+        <v>0.171985572282301</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.8608809945209422</v>
+        <v>0.8599278614115052</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.02741132126892678</v>
+        <v>0.0271257890831884</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>23505.73866433334</v>
+        <v>23504.714352</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.006491673118550851</v>
+        <v>0.006491390230149246</v>
       </c>
     </row>
     <row r="25">
@@ -989,19 +989,19 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.1828738984561135</v>
+        <v>0.1831992789879466</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.9143694922805677</v>
+        <v>0.9159963949397327</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.005399982475536585</v>
+        <v>0.005634536711941443</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>4961.076025500001</v>
+        <v>5054.612311291668</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.001169773487410741</v>
+        <v>0.001191828434093188</v>
       </c>
     </row>
     <row r="26">
@@ -1011,19 +1011,19 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.1473881771126137</v>
+        <v>0.147474100682104</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.7369408855630686</v>
+        <v>0.7373705034105198</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.02785476964453</v>
+        <v>0.02854494403873988</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>24850.71953545184</v>
+        <v>25046.56049175001</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.006797810292967059</v>
+        <v>0.006851381766686721</v>
       </c>
     </row>
     <row r="27">
@@ -1033,19 +1033,19 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.1335741832675398</v>
+        <v>0.1339438048709412</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.6678709163376991</v>
+        <v>0.6697190243547059</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.04194970664046396</v>
+        <v>0.04225645396670462</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>41351.9238226961</v>
+        <v>41202.70365895193</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.01627375387645947</v>
+        <v>0.01621502934822253</v>
       </c>
     </row>
     <row r="28">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.200445728873049</v>
+        <v>0.2005775302430081</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1.002228644365245</v>
+        <v>1.00288765121504</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.09654389320401623</v>
+        <v>0.09520462924697055</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>67930.49684490827</v>
+        <v>67924.17020990828</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.02905847128445086</v>
+        <v>0.02905576495445163</v>
       </c>
     </row>
     <row r="29">
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.3000077252085593</v>
+        <v>0.3002235222482208</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1.500038626042797</v>
+        <v>1.501117611241104</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.183864225114019</v>
+        <v>0.178255965124473</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>100400.0771837554</v>
+        <v>100522.7794677849</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.05339309915983015</v>
+        <v>0.05345835264769683</v>
       </c>
     </row>
     <row r="30">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.2555159253650321</v>
+        <v>0.2555166825223237</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1.277579626825161</v>
+        <v>1.277583412611618</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.1394747224462796</v>
+        <v>0.1404741614681833</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>82958.27768549827</v>
+        <v>83327.51171799251</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.04226461035430898</v>
+        <v>0.04245272337869072</v>
       </c>
     </row>
     <row r="31">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.2417199043547115</v>
+        <v>0.2417031264804596</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1.208599521773557</v>
+        <v>1.208515632402298</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.08759928236310492</v>
+        <v>0.08959662312834732</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>65401.73881691042</v>
+        <v>65677.21065755325</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.02846646842412885</v>
+        <v>0.02858636906584342</v>
       </c>
     </row>
     <row r="32">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.3084101360387435</v>
+        <v>0.3086835540187856</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1.542050680193717</v>
+        <v>1.543417770093928</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.05517166215190767</v>
+        <v>0.05634578217010736</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>54346.91297311675</v>
+        <v>54165.91201288925</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.02000426137906255</v>
+        <v>0.01993763771416289</v>
       </c>
     </row>
     <row r="33">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.2700442971692155</v>
+        <v>0.2701125464895269</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1.350221485846078</v>
+        <v>1.350562732447634</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.02195112932523458</v>
+        <v>0.02244585780367472</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>43086.57672485191</v>
+        <v>43882.47429183333</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.01081529590516879</v>
+        <v>0.01101507663391123</v>
       </c>
     </row>
     <row r="34">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.2470992362514883</v>
+        <v>0.2467086864657368</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1.235496181257441</v>
+        <v>1.233543432328684</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.0313393487851536</v>
+        <v>0.03149936615122747</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>56610.06355938326</v>
+        <v>57058.62844308902</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.01339525018150845</v>
+        <v>0.01350139100633856</v>
       </c>
     </row>
     <row r="35">
@@ -1209,19 +1209,19 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.2199483814758137</v>
+        <v>0.2199041106155841</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1.099741907379068</v>
+        <v>1.099520553077921</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.04851319129978881</v>
+        <v>0.04980178853767837</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>61235.00307225001</v>
+        <v>61230.59506463085</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.01694762589159322</v>
+        <v>0.01694640591510414</v>
       </c>
     </row>
     <row r="36">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.2029909949064889</v>
+        <v>0.2027082500931786</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1.014954974532444</v>
+        <v>1.013541250465893</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-0.001524668424752511</v>
+        <v>-0.001955791435455164</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>7364.248330250002</v>
+        <v>7371.930672750002</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.001987675518360346</v>
+        <v>0.00198974905029818</v>
       </c>
     </row>
     <row r="37">
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.1821814767902196</v>
+        <v>0.1816523810099644</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.910907383951098</v>
+        <v>0.908261905049822</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>-0.004767203097243841</v>
+        <v>-0.003611304587462149</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>6342.187977708337</v>
+        <v>6372.405191541669</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.001509879960389451</v>
+        <v>0.001517073749943799</v>
       </c>
     </row>
   </sheetData>
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2762573303438485</v>
+        <v>0.2763767734161043</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.381286651719243</v>
+        <v>1.381883867080522</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.009862392972247181</v>
+        <v>0.009953098942968013</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.007720679502288893</v>
+        <v>0.00772807729349745</v>
       </c>
     </row>
     <row r="3">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.24200964424526</v>
+        <v>0.2420049800943189</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.2100482212263</v>
+        <v>1.210024900471595</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.02254217765269077</v>
+        <v>0.02256881836590571</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.01230206684399515</v>
+        <v>0.01227560638682377</v>
       </c>
     </row>
     <row r="4">
@@ -1362,16 +1362,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2232856160072505</v>
+        <v>0.2233336735307066</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.116428080036252</v>
+        <v>1.116668367653533</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.03954967126742035</v>
+        <v>0.03996356328415547</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.01648356034242582</v>
+        <v>0.01653487039089029</v>
       </c>
     </row>
     <row r="5">
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.241871177504544</v>
+        <v>0.2419177588797677</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.20935588752272</v>
+        <v>1.209588794398839</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.01744355049129132</v>
+        <v>0.01757295911613359</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.01192064984990754</v>
+        <v>0.01193015265335862</v>
       </c>
     </row>
   </sheetData>

--- a/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
+++ b/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
@@ -439,7 +439,7 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2997203031524047</v>
+        <v>0.263675777518445</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.498601515762024</v>
+        <v>1.318378887592225</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.005168931257677989</v>
+        <v>0.004345044875881067</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>13230.94449745833</v>
+        <v>9405.162699569948</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.003097551663323235</v>
+        <v>0.002201881911716506</v>
       </c>
     </row>
     <row r="3">
@@ -505,19 +505,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.227697995930277</v>
+        <v>0.222007126472999</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.138489979651385</v>
+        <v>1.110035632364995</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.009883412598133585</v>
+        <v>0.00949050576518721</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>17621.6257228725</v>
+        <v>17113.12137830048</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.005308713975096989</v>
+        <v>0.005155521292260515</v>
       </c>
     </row>
     <row r="4">
@@ -527,19 +527,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2758927295067184</v>
+        <v>0.2756206925418705</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.379463647533592</v>
+        <v>1.378103462709352</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.01998801386816578</v>
+        <v>0.0199076201567567</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>31259.00852703533</v>
+        <v>31178.39483576571</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.009886380450870799</v>
+        <v>0.009860884516770673</v>
       </c>
     </row>
     <row r="5">
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.3813217175427082</v>
+        <v>0.2599189305431779</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.906608587713541</v>
+        <v>1.299594652715889</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.04819778871982623</v>
+        <v>0.03088452851243537</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>62397.20397856925</v>
+        <v>38283.09974154155</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.03017724965520669</v>
+        <v>0.01851491068209509</v>
       </c>
     </row>
     <row r="6">
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.3036777259695075</v>
+        <v>0.2258117128469622</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.518388629847538</v>
+        <v>1.129058564234811</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.0533249176301254</v>
+        <v>0.04574456090451144</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>49277.66149122542</v>
+        <v>17448.78744235873</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.01749737987247896</v>
+        <v>0.006195668644857585</v>
       </c>
     </row>
     <row r="7">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.3526902062099536</v>
+        <v>0.2784457233834937</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1.763451031049768</v>
+        <v>1.392228616917468</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.04272188407356232</v>
+        <v>0.03941679639579172</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>47892.37840362501</v>
+        <v>33111.11576248286</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.02121388494568851</v>
+        <v>0.01466653825978119</v>
       </c>
     </row>
     <row r="8">
@@ -615,19 +615,19 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.1770574448165846</v>
+        <v>0.1569073733546826</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.8852872240829228</v>
+        <v>0.7845368667734128</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.003906979036475333</v>
+        <v>0.003930968081598677</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>15819.995748655</v>
+        <v>14204.08750349283</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.003576721985432261</v>
+        <v>0.003211383420318919</v>
       </c>
     </row>
     <row r="9">
@@ -637,19 +637,19 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.3431448157787283</v>
+        <v>0.3087565298921736</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1.715724078893642</v>
+        <v>1.543782649460868</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.005033554592624196</v>
+        <v>0.0051795718694183</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>17814.36560370833</v>
+        <v>17704.83072946081</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.003414947400261382</v>
+        <v>0.003393949973669235</v>
       </c>
     </row>
     <row r="10">
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.3673031120633016</v>
+        <v>0.2775141286259727</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.836515560316508</v>
+        <v>1.387570643129864</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.01495614367621184</v>
+        <v>0.01325479469268098</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>25267.96890148825</v>
+        <v>24636.81184695452</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.006600100172730499</v>
+        <v>0.006435239284984085</v>
       </c>
     </row>
     <row r="11">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.2209584831305381</v>
+        <v>0.2140972365192453</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1.104792415652691</v>
+        <v>1.070486182596226</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.01326562505672426</v>
+        <v>0.01275712335712467</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>36153.68492148817</v>
+        <v>35435.33229112299</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.008400086381142677</v>
+        <v>0.008233181564654607</v>
       </c>
     </row>
     <row r="12">
@@ -703,19 +703,19 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.1992975838182589</v>
+        <v>0.1912562239546321</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.9964879190912946</v>
+        <v>0.9562811197731604</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.006337750218607837</v>
+        <v>0.006275943540237482</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>15936.5783690295</v>
+        <v>13998.07156505715</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.004010677762409398</v>
+        <v>0.003522823597547993</v>
       </c>
     </row>
     <row r="13">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.2075551359136039</v>
+        <v>0.2186523431303917</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1.03777567956802</v>
+        <v>1.093261715651958</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.002761549537777851</v>
+        <v>0.003082215855982615</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7465.91886104167</v>
+        <v>7724.53610315267</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.00170710489322188</v>
+        <v>0.001766238506605087</v>
       </c>
     </row>
     <row r="14">
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.416862015320279</v>
+        <v>0.3873571409881378</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2.084310076601395</v>
+        <v>1.936785704940689</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.008850101150716114</v>
+        <v>0.007681226004715292</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>18875.12474734484</v>
+        <v>17689.15594142443</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.004891764902421569</v>
+        <v>0.004584403724266474</v>
       </c>
     </row>
     <row r="15">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.2229038768359136</v>
+        <v>0.2665916011698903</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.114519384179568</v>
+        <v>1.332958005849451</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.02227431473470587</v>
+        <v>0.02700206270284339</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>28087.55551670834</v>
+        <v>33914.15092520486</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.00898298390238661</v>
+        <v>0.01084645018834049</v>
       </c>
     </row>
     <row r="16">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.2406992030632521</v>
+        <v>0.2542911641386682</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1.20349601531626</v>
+        <v>1.271455820693341</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.09870638990650184</v>
+        <v>0.1039370956673044</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>65055.26629991668</v>
+        <v>48302.12376550667</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.02877048183021453</v>
+        <v>0.02136145854433406</v>
       </c>
     </row>
     <row r="17">
@@ -813,19 +813,19 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.2630533589445115</v>
+        <v>0.2179213666731167</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1.315266794722558</v>
+        <v>1.089606833365584</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.1201133840188465</v>
+        <v>0.1139130042165444</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>78890.81363758877</v>
+        <v>37472.13948725507</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.04114035724198368</v>
+        <v>0.01954114977453584</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.2672783238260033</v>
+        <v>0.227580361245051</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1.336391619130016</v>
+        <v>1.137901806225255</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.1125483579082448</v>
+        <v>0.1034214520758282</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>92041.12714527968</v>
+        <v>29499.11057240737</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.05579121352082148</v>
+        <v>0.01788104109179096</v>
       </c>
     </row>
     <row r="19">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.2445197893704994</v>
+        <v>0.2242528128906831</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1.222598946852497</v>
+        <v>1.121264064453416</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.05329477027163858</v>
+        <v>0.049763994961498</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>53822.08270374483</v>
+        <v>33207.03870177583</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.0202694088485233</v>
+        <v>0.01250577848872799</v>
       </c>
     </row>
     <row r="20">
@@ -879,19 +879,19 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.1781779437415121</v>
+        <v>0.1639205917881648</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.8908897187075603</v>
+        <v>0.8196029589408237</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.01108254495932466</v>
+        <v>0.01007978460134161</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>22877.97830645834</v>
+        <v>27832.68585976213</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.004899593910370451</v>
+        <v>0.005960704058769392</v>
       </c>
     </row>
     <row r="21">
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.3126772377182015</v>
+        <v>0.2656076152068474</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1.563386188591007</v>
+        <v>1.328038076034237</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.02219170999381749</v>
+        <v>0.01880176564876889</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>26232.25888198125</v>
+        <v>35404.62326022354</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.006087866975325326</v>
+        <v>0.008216548856484552</v>
       </c>
     </row>
     <row r="22">
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.2361198048629374</v>
+        <v>0.2261535402363856</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1.180599024314687</v>
+        <v>1.130767701181928</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.02711344606662317</v>
+        <v>0.02487486491914699</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>36187.03415104167</v>
+        <v>39961.66497099679</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.008874618929942261</v>
+        <v>0.00980032093659187</v>
       </c>
     </row>
     <row r="23">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.2314311704253437</v>
+        <v>0.2087135097448347</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1.157155852126719</v>
+        <v>1.043567548724174</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.02806627729492727</v>
+        <v>0.02406413973405815</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>47470.820071934</v>
+        <v>42579.24534785701</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.01133133386492229</v>
+        <v>0.01016370991741644</v>
       </c>
     </row>
     <row r="24">
@@ -967,19 +967,19 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.171985572282301</v>
+        <v>0.1686251920194921</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.8599278614115052</v>
+        <v>0.8431259600974604</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.0271257890831884</v>
+        <v>0.02614844010933876</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>23504.714352</v>
+        <v>29232.23820497794</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.006491390230149246</v>
+        <v>0.008073183219648145</v>
       </c>
     </row>
     <row r="25">
@@ -989,19 +989,19 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.1831992789879466</v>
+        <v>0.1956313751857069</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.9159963949397327</v>
+        <v>0.9781568759285347</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.005634536711941443</v>
+        <v>0.006413335018216191</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>5054.612311291668</v>
+        <v>9514.95685349917</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.001191828434093188</v>
+        <v>0.002243534306644431</v>
       </c>
     </row>
     <row r="26">
@@ -1011,19 +1011,19 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.147474100682104</v>
+        <v>0.2064422081368226</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.7373705034105198</v>
+        <v>1.032211040684113</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.02854494403873988</v>
+        <v>0.04306944465538474</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>25046.56049175001</v>
+        <v>50856.84833994089</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.006851381766686721</v>
+        <v>0.01391167795443187</v>
       </c>
     </row>
     <row r="27">
@@ -1033,19 +1033,19 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.1339438048709412</v>
+        <v>0.1453905560983402</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.6697190243547059</v>
+        <v>0.7269527804917012</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.04225645396670462</v>
+        <v>0.04674058543121219</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>41202.70365895193</v>
+        <v>39249.66548547393</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.01621502934822253</v>
+        <v>0.01544642514294329</v>
       </c>
     </row>
     <row r="28">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.2005775302430081</v>
+        <v>0.2171316866786955</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1.00288765121504</v>
+        <v>1.085658433393478</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.09520462924697055</v>
+        <v>0.1027633698245287</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>67924.17020990828</v>
+        <v>36224.31164191721</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.02905576495445163</v>
+        <v>0.0154955898828311</v>
       </c>
     </row>
     <row r="29">
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.3002235222482208</v>
+        <v>0.2460554272674296</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1.501117611241104</v>
+        <v>1.230277136337148</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.178255965124473</v>
+        <v>0.1362465764826644</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>100522.7794677849</v>
+        <v>37708.46903067731</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.05345835264769683</v>
+        <v>0.02005349081988652</v>
       </c>
     </row>
     <row r="30">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.2555166825223237</v>
+        <v>0.2189075579501914</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1.277583412611618</v>
+        <v>1.094537789750957</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.1404741614681833</v>
+        <v>0.1182852478247853</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>83327.51171799251</v>
+        <v>46018.43208777625</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.04245272337869072</v>
+        <v>0.02344493106136514</v>
       </c>
     </row>
     <row r="31">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.2417031264804596</v>
+        <v>0.1811958236773696</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1.208515632402298</v>
+        <v>0.9059791183868481</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.08959662312834732</v>
+        <v>0.06130524841016678</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>65677.21065755325</v>
+        <v>32168.02851176483</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.02858636906584342</v>
+        <v>0.0140013122657201</v>
       </c>
     </row>
     <row r="32">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.3086835540187856</v>
+        <v>0.2459538398105746</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1.543417770093928</v>
+        <v>1.229769199052873</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.05634578217010736</v>
+        <v>0.04780005040809816</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>54165.91201288925</v>
+        <v>40118.85735567496</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.01993763771416289</v>
+        <v>0.01476713330836724</v>
       </c>
     </row>
     <row r="33">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.2701125464895269</v>
+        <v>0.2319364255947153</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1.350562732447634</v>
+        <v>1.159682127973577</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.02244585780367472</v>
+        <v>0.02111549294839558</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>43882.47429183333</v>
+        <v>41311.51584770624</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.01101507663391123</v>
+        <v>0.01036973234233076</v>
       </c>
     </row>
     <row r="34">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.2467086864657368</v>
+        <v>0.2243185504971884</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1.233543432328684</v>
+        <v>1.121592752485942</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.03149936615122747</v>
+        <v>0.02709366346202628</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>57058.62844308902</v>
+        <v>44078.12190475292</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.01350139100633856</v>
+        <v>0.01042990297698274</v>
       </c>
     </row>
     <row r="35">
@@ -1209,19 +1209,19 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.2199041106155841</v>
+        <v>0.2013025995483013</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1.099520553077921</v>
+        <v>1.006512997741506</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.04980178853767837</v>
+        <v>0.0431894344598051</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>61230.59506463085</v>
+        <v>45786.69494237297</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.01694640591510414</v>
+        <v>0.01267209500716904</v>
       </c>
     </row>
     <row r="36">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.2027082500931786</v>
+        <v>0.2338707427750077</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1.013541250465893</v>
+        <v>1.169353713875039</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>-0.001955791435455164</v>
+        <v>0.002054580792010413</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>7371.930672750002</v>
+        <v>2455.825584072853</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.00198974905029818</v>
+        <v>0.0006628489659662106</v>
       </c>
     </row>
     <row r="37">
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.1816523810099644</v>
+        <v>0.2330673390717352</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.908261905049822</v>
+        <v>1.165336695358676</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>-0.003611304587462149</v>
+        <v>0.0005754800347328473</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>6372.405191541669</v>
+        <v>404.180344037828</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.001517073749943799</v>
+        <v>9.622291297435511e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2763767734161043</v>
+        <v>0.2379127774724447</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.381883867080522</v>
+        <v>1.189563887362224</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.009953098942968013</v>
+        <v>0.008849339905411589</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.00772807729349745</v>
+        <v>0.005912849109732226</v>
       </c>
     </row>
     <row r="3">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.2420049800943189</v>
+        <v>0.2268991574016179</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.210024900471595</v>
+        <v>1.13449578700809</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.02256881836590571</v>
+        <v>0.02139641747624443</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.01227560638682377</v>
+        <v>0.009478651154725367</v>
       </c>
     </row>
     <row r="4">
@@ -1362,16 +1362,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2233336735307066</v>
+        <v>0.2112318986579491</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.116668367653533</v>
+        <v>1.056159493289745</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.03996356328415547</v>
+        <v>0.03820807936071291</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.01653487039089029</v>
+        <v>0.01121700402947787</v>
       </c>
     </row>
     <row r="5">
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.2419177588797677</v>
+        <v>0.2227165182726689</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.209588794398839</v>
+        <v>1.113582591363345</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.01757295911613359</v>
+        <v>0.01634825093840044</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.01193015265335862</v>
+        <v>0.008719356721346178</v>
       </c>
     </row>
   </sheetData>

--- a/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
+++ b/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
@@ -439,9 +439,9 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -483,19 +483,19 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.263675777518445</v>
+        <v>0.2660582695402848</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.318378887592225</v>
+        <v>1.330291347701424</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.004345044875881067</v>
+        <v>0.004340458395462042</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>9405.162699569948</v>
+        <v>9417.666359432507</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.002201881911716506</v>
+        <v>0.00220480919573711</v>
       </c>
     </row>
     <row r="3">
@@ -505,19 +505,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.222007126472999</v>
+        <v>0.222426917468602</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.110035632364995</v>
+        <v>1.11213458734301</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.00949050576518721</v>
+        <v>0.009497391694645215</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>17113.12137830048</v>
+        <v>17117.24621696328</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.005155521292260515</v>
+        <v>0.005156763946542169</v>
       </c>
     </row>
     <row r="4">
@@ -527,19 +527,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2756206925418705</v>
+        <v>0.2760640656771063</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.378103462709352</v>
+        <v>1.380320328385531</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.0199076201567567</v>
+        <v>0.01998902807858755</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>31178.39483576571</v>
+        <v>31295.51444718265</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.009860884516770673</v>
+        <v>0.00989792628780844</v>
       </c>
     </row>
     <row r="5">
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.2599189305431779</v>
+        <v>0.261626218015282</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.299594652715889</v>
+        <v>1.30813109007641</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.03088452851243537</v>
+        <v>0.03095202446322005</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>38283.09974154155</v>
+        <v>38357.46213922463</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.01851491068209509</v>
+        <v>0.01855087467561975</v>
       </c>
     </row>
     <row r="6">
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.2258117128469622</v>
+        <v>0.226645351123725</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1.129058564234811</v>
+        <v>1.133226755618625</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.04574456090451144</v>
+        <v>0.04571865204805327</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>17448.78744235873</v>
+        <v>17434.09225065517</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.006195668644857585</v>
+        <v>0.006190450715602116</v>
       </c>
     </row>
     <row r="7">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.2784457233834937</v>
+        <v>0.2793299729450691</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1.392228616917468</v>
+        <v>1.396649864725345</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.03941679639579172</v>
+        <v>0.03957496193164937</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>33111.11576248286</v>
+        <v>33248.96171744925</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.01466653825978119</v>
+        <v>0.01472759699869453</v>
       </c>
     </row>
     <row r="8">
@@ -615,19 +615,19 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.1569073733546826</v>
+        <v>0.1591332798167239</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.7845368667734128</v>
+        <v>0.7956663990836196</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.003930968081598677</v>
+        <v>0.00384815913916707</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>14204.08750349283</v>
+        <v>13901.49823493324</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.003211383420318919</v>
+        <v>0.003142971411453179</v>
       </c>
     </row>
     <row r="9">
@@ -637,19 +637,19 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.3087565298921736</v>
+        <v>0.3108656825222525</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1.543782649460868</v>
+        <v>1.554328412611262</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.0051795718694183</v>
+        <v>0.005212596065183583</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>17704.83072946081</v>
+        <v>17804.81009703921</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.003393949973669235</v>
+        <v>0.003413115645295541</v>
       </c>
     </row>
     <row r="10">
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.2775141286259727</v>
+        <v>0.2783916632800361</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.387570643129864</v>
+        <v>1.39195831640018</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.01325479469268098</v>
+        <v>0.01294546938112249</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>24636.81184695452</v>
+        <v>24073.74640024058</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.006435239284984085</v>
+        <v>0.006288164212721495</v>
       </c>
     </row>
     <row r="11">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.2140972365192453</v>
+        <v>0.2144456480014621</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1.070486182596226</v>
+        <v>1.07222824000731</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.01275712335712467</v>
+        <v>0.01273419124806325</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>35435.33229112299</v>
+        <v>35380.04411903257</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.008233181564654607</v>
+        <v>0.00822033569783844</v>
       </c>
     </row>
     <row r="12">
@@ -703,19 +703,19 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.1912562239546321</v>
+        <v>0.1919168851040352</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.9562811197731604</v>
+        <v>0.9595844255201758</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.006275943540237482</v>
+        <v>0.006263827738836113</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>13998.07156505715</v>
+        <v>13999.3796274052</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.003522823597547993</v>
+        <v>0.003523152790957625</v>
       </c>
     </row>
     <row r="13">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.2186523431303917</v>
+        <v>0.2180465923312817</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1.093261715651958</v>
+        <v>1.090232961656409</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.003082215855982615</v>
+        <v>0.003054372145070072</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7724.53610315267</v>
+        <v>7632.756424198393</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.001766238506605087</v>
+        <v>0.001745252805855144</v>
       </c>
     </row>
     <row r="14">
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.3873571409881378</v>
+        <v>0.3880820687023163</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1.936785704940689</v>
+        <v>1.940410343511581</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.007681226004715292</v>
+        <v>0.00765704403581372</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17689.15594142443</v>
+        <v>17637.98043315811</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.004584403724266474</v>
+        <v>0.004571140842110638</v>
       </c>
     </row>
     <row r="15">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.2665916011698903</v>
+        <v>0.2667589079123795</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.332958005849451</v>
+        <v>1.333794539561897</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.02700206270284339</v>
+        <v>0.02701295435276562</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>33914.15092520486</v>
+        <v>33933.9244446801</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.01084645018834049</v>
+        <v>0.01085277417075448</v>
       </c>
     </row>
     <row r="16">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.2542911641386682</v>
+        <v>0.2545329001878118</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1.271455820693341</v>
+        <v>1.272664500939059</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.1039370956673044</v>
+        <v>0.1035385943115837</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>48302.12376550667</v>
+        <v>48113.76676526596</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.02136145854433406</v>
+        <v>0.02127815826810376</v>
       </c>
     </row>
     <row r="17">
@@ -813,19 +813,19 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.2179213666731167</v>
+        <v>0.2183152313254422</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1.089606833365584</v>
+        <v>1.091576156627211</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.1139130042165444</v>
+        <v>0.1119024456535446</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>37472.13948725507</v>
+        <v>36811.90562309476</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.01954114977453584</v>
+        <v>0.0191968478744491</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>0.227580361245051</v>
+        <v>0.2275769209074074</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1.137901806225255</v>
+        <v>1.137884604537037</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.1034214520758282</v>
+        <v>0.1027064566613239</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>29499.11057240737</v>
+        <v>29295.7898374772</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.01788104109179096</v>
+        <v>0.01775779715848064</v>
       </c>
     </row>
     <row r="19">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.2242528128906831</v>
+        <v>0.2241887733233073</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1.121264064453416</v>
+        <v>1.120943866616536</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.049763994961498</v>
+        <v>0.04884742171085944</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>33207.03870177583</v>
+        <v>32595.46967576235</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.01250577848872799</v>
+        <v>0.01227546145147038</v>
       </c>
     </row>
     <row r="20">
@@ -879,19 +879,19 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.1639205917881648</v>
+        <v>0.1667661561605587</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.8196029589408237</v>
+        <v>0.8338307808027936</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.01007978460134161</v>
+        <v>0.01004915003566171</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>27832.68585976213</v>
+        <v>27756.48257825524</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.005960704058769392</v>
+        <v>0.005944384210528429</v>
       </c>
     </row>
     <row r="21">
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.2656076152068474</v>
+        <v>0.2656289812873456</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1.328038076034237</v>
+        <v>1.328144906436728</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.01880176564876889</v>
+        <v>0.01889121296349402</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>35404.62326022354</v>
+        <v>35534.2330256165</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.008216548856484552</v>
+        <v>0.008246628119348089</v>
       </c>
     </row>
     <row r="22">
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.2261535402363856</v>
+        <v>0.2263447316982285</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1.130767701181928</v>
+        <v>1.131723658491142</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.02487486491914699</v>
+        <v>0.02533804296830943</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>39961.66497099679</v>
+        <v>40695.11838112678</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.00980032093659187</v>
+        <v>0.009980195294092456</v>
       </c>
     </row>
     <row r="23">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.2087135097448347</v>
+        <v>0.2092425980335309</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1.043567548724174</v>
+        <v>1.046212990167654</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.02406413973405815</v>
+        <v>0.02454439132798581</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>42579.24534785701</v>
+        <v>43460.58792427857</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.01016370991741644</v>
+        <v>0.01037408730225349</v>
       </c>
     </row>
     <row r="24">
@@ -967,19 +967,19 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.1686251920194921</v>
+        <v>0.1689198907266411</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.8431259600974604</v>
+        <v>0.8445994536332054</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.02614844010933876</v>
+        <v>0.02608386901064053</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>29232.23820497794</v>
+        <v>29141.94433738897</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.008073183219648145</v>
+        <v>0.008048246403946762</v>
       </c>
     </row>
     <row r="25">
@@ -989,19 +989,19 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.1956313751857069</v>
+        <v>0.1974074246407309</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.9781568759285347</v>
+        <v>0.9870371232036546</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.006413335018216191</v>
+        <v>0.00656253138839626</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>9514.95685349917</v>
+        <v>9739.054404133232</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.002243534306644431</v>
+        <v>0.002296374330054271</v>
       </c>
     </row>
     <row r="26">
@@ -1011,19 +1011,19 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.2064422081368226</v>
+        <v>0.2073717485820583</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1.032211040684113</v>
+        <v>1.036858742910292</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.04306944465538474</v>
+        <v>0.04290519077631972</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>50856.84833994089</v>
+        <v>50666.49235914159</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.01391167795443187</v>
+        <v>0.01385960687279742</v>
       </c>
     </row>
     <row r="27">
@@ -1033,19 +1033,19 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.1453905560983402</v>
+        <v>0.1454923233705334</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.7269527804917012</v>
+        <v>0.7274616168526672</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.04674058543121219</v>
+        <v>0.04542865511481419</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>39249.66548547393</v>
+        <v>38131.90511435154</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.01544642514294329</v>
+        <v>0.01500653854297519</v>
       </c>
     </row>
     <row r="28">
@@ -1055,19 +1055,19 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.2171316866786955</v>
+        <v>0.217661526039657</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1.085658433393478</v>
+        <v>1.088307630198285</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.1027633698245287</v>
+        <v>0.1078401764613783</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>36224.31164191721</v>
+        <v>38005.24719258782</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.0154955898828311</v>
+        <v>0.01625741655806907</v>
       </c>
     </row>
     <row r="29">
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.2460554272674296</v>
+        <v>0.2481407038589025</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1.230277136337148</v>
+        <v>1.240703519294513</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.1362465764826644</v>
+        <v>0.1328911995670021</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>37708.46903067731</v>
+        <v>36811.41180888616</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.02005349081988652</v>
+        <v>0.01957643276835261</v>
       </c>
     </row>
     <row r="30">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.2189075579501914</v>
+        <v>0.2189758253770351</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1.094537789750957</v>
+        <v>1.094879126885175</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.1182852478247853</v>
+        <v>0.1169538806985804</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>46018.43208777625</v>
+        <v>45488.27862411248</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.02344493106136514</v>
+        <v>0.02317483469250509</v>
       </c>
     </row>
     <row r="31">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.1811958236773696</v>
+        <v>0.1809181700969195</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>0.9059791183868481</v>
+        <v>0.9045908504845974</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.06130524841016678</v>
+        <v>0.05840869634115225</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>32168.02851176483</v>
+        <v>30676.82280907984</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.0140013122657201</v>
+        <v>0.01335225673879904</v>
       </c>
     </row>
     <row r="32">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.2459538398105746</v>
+        <v>0.2462220423681505</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1.229769199052873</v>
+        <v>1.231110211840753</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.04780005040809816</v>
+        <v>0.04728352846993988</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>40118.85735567496</v>
+        <v>39710.83293060772</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.01476713330836724</v>
+        <v>0.01461694580365793</v>
       </c>
     </row>
     <row r="33">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.2319364255947153</v>
+        <v>0.2356130335260537</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1.159682127973577</v>
+        <v>1.178065167630268</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.02111549294839558</v>
+        <v>0.0213984486284778</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>41311.51584770624</v>
+        <v>41865.67339496245</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.01036973234233076</v>
+        <v>0.01050883315532716</v>
       </c>
     </row>
     <row r="34">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.2243185504971884</v>
+        <v>0.2249419876613653</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1.121592752485942</v>
+        <v>1.124709938306826</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.02709366346202628</v>
+        <v>0.02718386663399109</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>44078.12190475292</v>
+        <v>44226.96255865344</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.01042990297698274</v>
+        <v>0.01046512211772942</v>
       </c>
     </row>
     <row r="35">
@@ -1209,19 +1209,19 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.2013025995483013</v>
+        <v>0.2017536488627103</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1.006512997741506</v>
+        <v>1.008768244313551</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.0431894344598051</v>
+        <v>0.04372221156634065</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>45786.69494237297</v>
+        <v>46311.51283437619</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.01267209500716904</v>
+        <v>0.01281734554768736</v>
       </c>
     </row>
     <row r="36">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0.2338707427750077</v>
+        <v>0.234835169979787</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1.169353713875039</v>
+        <v>1.174175849898935</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.002054580792010413</v>
+        <v>0.00185833844612147</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2455.825584072853</v>
+        <v>2223.439635714283</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.0006628489659662106</v>
+        <v>0.0006001259507107489</v>
       </c>
     </row>
     <row r="37">
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.2330673390717352</v>
+        <v>0.2332902480535446</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1.165336695358676</v>
+        <v>1.166451240267723</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.0005754800347328473</v>
+        <v>-0.0004333285980325177</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>404.180344037828</v>
+        <v>-307.7871420019073</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>9.622291297435511e-05</v>
+        <v>-7.327465527790033e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1324,16 +1324,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2379127774724447</v>
+        <v>0.2390521776954898</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.189563887362224</v>
+        <v>1.195260888477449</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.008849339905411589</v>
+        <v>0.008835497283213624</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.005912849109732226</v>
+        <v>0.005899667291641209</v>
       </c>
     </row>
     <row r="3">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.2268991574016179</v>
+        <v>0.2274898096274938</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1.13449578700809</v>
+        <v>1.137449048137469</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.02139641747624443</v>
+        <v>0.02141152274315095</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.009478651154725367</v>
+        <v>0.00948129120294694</v>
       </c>
     </row>
     <row r="4">
@@ -1362,16 +1362,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.2112318986579491</v>
+        <v>0.2119928205566187</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.056159493289745</v>
+        <v>1.059964102783094</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.03820807936071291</v>
+        <v>0.03796827617847924</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.01121700402947787</v>
+        <v>0.01114776579154231</v>
       </c>
     </row>
     <row r="5">
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.2227165182726689</v>
+        <v>0.2235067697284544</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1.113582591363345</v>
+        <v>1.117533848642272</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.01634825093840044</v>
+        <v>0.01630391269788673</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.008719356721346178</v>
+        <v>0.008694352960265541</v>
       </c>
     </row>
   </sheetData>

--- a/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
+++ b/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
@@ -9,12 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Analysis" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annual Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Carbon Emission" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Monthly Analysis'!$A$1:$F$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Annual Summary'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Monthly Carbon Emission'!$A$1:$B$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +493,7 @@
         <v>9417.666359432507</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.00220480919573711</v>
+        <v>0.004402249571369874</v>
       </c>
     </row>
     <row r="3">
@@ -517,7 +515,7 @@
         <v>17117.24621696328</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.005156763946542169</v>
+        <v>0.009495819002113383</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +537,7 @@
         <v>31295.51444718265</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.00989792628780844</v>
+        <v>0.01987422070597889</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +559,7 @@
         <v>38357.46213922463</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.01855087467561975</v>
+        <v>0.03078767535068412</v>
       </c>
     </row>
     <row r="6">
@@ -583,7 +581,7 @@
         <v>17434.09225065517</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.006190450715602116</v>
+        <v>0.04549652793788422</v>
       </c>
     </row>
     <row r="7">
@@ -605,7 +603,7 @@
         <v>33248.96171744925</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.01472759699869453</v>
+        <v>0.03946200279741553</v>
       </c>
     </row>
     <row r="8">
@@ -627,7 +625,7 @@
         <v>13901.49823493324</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.003142971411453179</v>
+        <v>0.003863945860667524</v>
       </c>
     </row>
     <row r="9">
@@ -649,7 +647,7 @@
         <v>17804.81009703921</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.003413115645295541</v>
+        <v>0.005270264702459821</v>
       </c>
     </row>
     <row r="10">
@@ -671,7 +669,7 @@
         <v>24073.74640024058</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.006288164212721495</v>
+        <v>0.01292037121966886</v>
       </c>
     </row>
     <row r="11">
@@ -693,7 +691,7 @@
         <v>35380.04411903257</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.00822033569783844</v>
+        <v>0.01275436892759566</v>
       </c>
     </row>
     <row r="12">
@@ -715,7 +713,7 @@
         <v>13999.3796274052</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.003523152790957625</v>
+        <v>0.006201885395254411</v>
       </c>
     </row>
     <row r="13">
@@ -737,7 +735,7 @@
         <v>7632.756424198393</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.001745252805855144</v>
+        <v>0.003042351828759242</v>
       </c>
     </row>
     <row r="14">
@@ -759,7 +757,7 @@
         <v>17637.98043315811</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.004571140842110638</v>
+        <v>0.00769350375380712</v>
       </c>
     </row>
     <row r="15">
@@ -781,7 +779,7 @@
         <v>33933.9244446801</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.01085277417075448</v>
+        <v>0.02712569691928253</v>
       </c>
     </row>
     <row r="16">
@@ -803,7 +801,7 @@
         <v>48113.76676526596</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.02127815826810376</v>
+        <v>0.1033945377079135</v>
       </c>
     </row>
     <row r="17">
@@ -825,7 +823,7 @@
         <v>36811.90562309476</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.0191968478744491</v>
+        <v>0.1118036641407157</v>
       </c>
     </row>
     <row r="18">
@@ -847,7 +845,7 @@
         <v>29295.7898374772</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.01775779715848064</v>
+        <v>0.1024889289131546</v>
       </c>
     </row>
     <row r="19">
@@ -869,7 +867,7 @@
         <v>32595.46967576235</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.01227546145147038</v>
+        <v>0.04872736072626074</v>
       </c>
     </row>
     <row r="20">
@@ -891,7 +889,7 @@
         <v>27756.48257825524</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.005944384210528429</v>
+        <v>0.01013892492766191</v>
       </c>
     </row>
     <row r="21">
@@ -913,7 +911,7 @@
         <v>35534.2330256165</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.008246628119348089</v>
+        <v>0.01878376528503781</v>
       </c>
     </row>
     <row r="22">
@@ -935,7 +933,7 @@
         <v>40695.11838112678</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.009980195294092456</v>
+        <v>0.02534699317900928</v>
       </c>
     </row>
     <row r="23">
@@ -957,7 +955,7 @@
         <v>43460.58792427857</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.01037408730225349</v>
+        <v>0.02437733635667043</v>
       </c>
     </row>
     <row r="24">
@@ -979,7 +977,7 @@
         <v>29141.94433738897</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.008048246403946762</v>
+        <v>0.02590862298367062</v>
       </c>
     </row>
     <row r="25">
@@ -1001,7 +999,7 @@
         <v>9739.054404133232</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.002296374330054271</v>
+        <v>0.006597644843243317</v>
       </c>
     </row>
     <row r="26">
@@ -1023,7 +1021,7 @@
         <v>50666.49235914159</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.01385960687279742</v>
+        <v>0.04280486563839878</v>
       </c>
     </row>
     <row r="27">
@@ -1045,7 +1043,7 @@
         <v>38131.90511435154</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.01500653854297519</v>
+        <v>0.04534990822425392</v>
       </c>
     </row>
     <row r="28">
@@ -1067,7 +1065,7 @@
         <v>38005.24719258782</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.01625741655806907</v>
+        <v>0.1079074911641977</v>
       </c>
     </row>
     <row r="29">
@@ -1089,7 +1087,7 @@
         <v>36811.41180888616</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.01957643276835261</v>
+        <v>0.1329723749001658</v>
       </c>
     </row>
     <row r="30">
@@ -1111,7 +1109,7 @@
         <v>45488.27862411248</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.02317483469250509</v>
+        <v>0.1169394943013584</v>
       </c>
     </row>
     <row r="31">
@@ -1133,7 +1131,7 @@
         <v>30676.82280907984</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.01335225673879904</v>
+        <v>0.05845990332803951</v>
       </c>
     </row>
     <row r="32">
@@ -1155,7 +1153,7 @@
         <v>39710.83293060772</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.01461694580365793</v>
+        <v>0.04727173971505261</v>
       </c>
     </row>
     <row r="33">
@@ -1177,7 +1175,7 @@
         <v>41865.67339496245</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.01050883315532716</v>
+        <v>0.02132743767136852</v>
       </c>
     </row>
     <row r="34">
@@ -1199,7 +1197,7 @@
         <v>44226.96255865344</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.01046512211772942</v>
+        <v>0.02713366807875624</v>
       </c>
     </row>
     <row r="35">
@@ -1221,7 +1219,7 @@
         <v>46311.51283437619</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.01281734554768736</v>
+        <v>0.04334769423104392</v>
       </c>
     </row>
     <row r="36">
@@ -1243,7 +1241,7 @@
         <v>2223.439635714283</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.0006001259507107489</v>
+        <v>0.002023967935993562</v>
       </c>
     </row>
     <row r="37">
@@ -1265,7 +1263,7 @@
         <v>-307.7871420019073</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-7.327465527790033e-05</v>
+        <v>-0.0004251562942802745</v>
       </c>
     </row>
   </sheetData>
@@ -1333,7 +1331,7 @@
         <v>0.008835497283213624</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.005899667291641209</v>
+        <v>0.01065608290109359</v>
       </c>
     </row>
     <row r="3">
@@ -1352,7 +1350,7 @@
         <v>0.02141152274315095</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.00948129120294694</v>
+        <v>0.02417835258795758</v>
       </c>
     </row>
     <row r="4">
@@ -1371,7 +1369,7 @@
         <v>0.03796827617847924</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.01114776579154231</v>
+        <v>0.03799510846530392</v>
       </c>
     </row>
     <row r="5">
@@ -1390,402 +1388,11 @@
         <v>0.01630391269788673</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.008694352960265541</v>
+        <v>0.02067974948778655</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>carbon emission</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>202301</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>4271420.12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>202302</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>3319377.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>202303</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>3161825.37</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>202304</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>2067690.22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>202305</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>2816288.03</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>202306</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>2257595.84</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>202307</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>4423043.17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>202308</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>5216585.65</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>202309</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>3828422.03</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>202310</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>4303965.85</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>202311</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>3973537.47</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>202312</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>4373438.85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>202401</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>3858551.08</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>202402</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>3126751.18</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>202403</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>2261180.98</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>202404</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>1917601.57</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>202405</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>1649742.34</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>202406</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>2655335.59</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>202407</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>4669362.14</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>202408</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>4308940.88</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>202409</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>4077587.38</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>202410</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>4189340.87</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>202411</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>3620906.08</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>202412</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>4241056.99</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>202501</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>3655694.77</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>202502</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>2541019.37</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>202503</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>2337717.5</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>202504</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>1880394.26</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>202505</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>1962830.77</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>202506</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>2297500.97</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>202507</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>2716766.79</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>202508</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>3983855.56</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>202509</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>4226129.62</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>202510</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>3613190.63</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>202511</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>3704954.99</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>202512</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>4200458.41</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B37"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
+++ b/Figure_Plot/figure_plot_4_d/analysis_202301_202512.xlsx
@@ -438,8 +438,8 @@
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -487,13 +487,13 @@
         <v>1.330291347701424</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.004340458395462042</v>
+        <v>0.002226929082644463</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>9417.666359432507</v>
+        <v>6030.255198530853</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.004402249571369874</v>
+        <v>0.002227464443548963</v>
       </c>
     </row>
     <row r="3">
@@ -509,13 +509,13 @@
         <v>1.11213458734301</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.009497391694645215</v>
+        <v>0.005118307263724987</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>17117.24621696328</v>
+        <v>12010.10362156713</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.009495819002113383</v>
+        <v>0.005135459777794257</v>
       </c>
     </row>
     <row r="4">
@@ -528,16 +528,16 @@
         <v>0.2760640656771063</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.380320328385531</v>
+        <v>1.380320328385532</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.01998902807858755</v>
+        <v>0.01039821138673899</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>31295.51444718265</v>
+        <v>22849.01879233867</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.01987422070597889</v>
+        <v>0.0104387122922281</v>
       </c>
     </row>
     <row r="5">
@@ -553,13 +553,13 @@
         <v>1.30813109007641</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.03095202446322005</v>
+        <v>0.01560968768756347</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>38357.46213922463</v>
+        <v>28716.64629165828</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.03078767535068412</v>
+        <v>0.01566484486620861</v>
       </c>
     </row>
     <row r="6">
@@ -575,13 +575,13 @@
         <v>1.133226755618625</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.04571865204805327</v>
+        <v>0.01866766569742678</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>17434.09225065517</v>
+        <v>21896.00852576643</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.04549652793788422</v>
+        <v>0.01863135586833444</v>
       </c>
     </row>
     <row r="7">
@@ -597,13 +597,13 @@
         <v>1.396649864725345</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.03957496193164937</v>
+        <v>0.01737079993356825</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>33248.96171744925</v>
+        <v>28341.16987153143</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.03946200279741553</v>
+        <v>0.01743857429186072</v>
       </c>
     </row>
     <row r="8">
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.1591332798167239</v>
+        <v>0.1591332798167237</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.7956663990836196</v>
+        <v>0.7956663990836185</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.00384815913916707</v>
+        <v>0.003410021660681348</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>13901.49823493324</v>
+        <v>12800.95874801232</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.003863945860667524</v>
+        <v>0.003403226289061767</v>
       </c>
     </row>
     <row r="9">
@@ -641,13 +641,13 @@
         <v>1.554328412611262</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.005212596065183583</v>
+        <v>0.003781442803530428</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>17804.81009703921</v>
+        <v>13872.82011251152</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.005270264702459821</v>
+        <v>0.003773899054349208</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.2783916632800361</v>
+        <v>0.2783916632800358</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.39195831640018</v>
+        <v>1.391958316400179</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.01294546938112249</v>
+        <v>0.005756378426396366</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>24073.74640024058</v>
+        <v>14477.31403232645</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.01292037121966886</v>
+        <v>0.005799814557415932</v>
       </c>
     </row>
     <row r="11">
@@ -685,13 +685,13 @@
         <v>1.07222824000731</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.01273419124806325</v>
+        <v>0.007678593885810915</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>35380.04411903257</v>
+        <v>24922.1509369202</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.01275436892759566</v>
+        <v>0.007695339164469617</v>
       </c>
     </row>
     <row r="12">
@@ -707,13 +707,13 @@
         <v>0.9595844255201758</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.006263827738836113</v>
+        <v>0.003392263820402934</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>13999.3796274052</v>
+        <v>9408.8097703401</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.006201885395254411</v>
+        <v>0.003363138023671406</v>
       </c>
     </row>
     <row r="13">
@@ -729,13 +729,13 @@
         <v>1.090232961656409</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.003054372145070072</v>
+        <v>0.0009121256329807751</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7632.756424198393</v>
+        <v>2719.824773468077</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.003042351828759242</v>
+        <v>0.0009289384865098954</v>
       </c>
     </row>
     <row r="14">
@@ -745,19 +745,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.3880820687023163</v>
+        <v>0.3880820687023164</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1.940410343511581</v>
+        <v>1.940410343511582</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.00765704403581372</v>
+        <v>0.003572760305959025</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17637.98043315811</v>
+        <v>9941.416859214194</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.00769350375380712</v>
+        <v>0.003618139247487282</v>
       </c>
     </row>
     <row r="15">
@@ -773,13 +773,13 @@
         <v>1.333794539561897</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.02701295435276562</v>
+        <v>0.0119662798694408</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>33933.9244446801</v>
+        <v>20972.15612662304</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.02712569691928253</v>
+        <v>0.01188646695648461</v>
       </c>
     </row>
     <row r="16">
@@ -789,19 +789,19 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.2545329001878118</v>
+        <v>0.254532900187812</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1.272664500939059</v>
+        <v>1.27266450093906</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.1035385943115837</v>
+        <v>0.04639662900585143</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>48113.76676526596</v>
+        <v>50131.33216708247</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.1033945377079135</v>
+        <v>0.04625788284072003</v>
       </c>
     </row>
     <row r="17">
@@ -817,13 +817,13 @@
         <v>1.091576156627211</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.1119024456535446</v>
+        <v>0.05604514215727111</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>36811.90562309476</v>
+        <v>48348.16931294801</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.1118036641407157</v>
+        <v>0.05600510975126709</v>
       </c>
     </row>
     <row r="18">
@@ -839,13 +839,13 @@
         <v>1.137884604537037</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.1027064566613239</v>
+        <v>0.07211787157161946</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>29295.7898374772</v>
+        <v>53416.06355780724</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.1024889289131546</v>
+        <v>0.07220237799018349</v>
       </c>
     </row>
     <row r="19">
@@ -855,19 +855,19 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.2241887733233073</v>
+        <v>0.2241887733233077</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1.120943866616536</v>
+        <v>1.120943866616539</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.04884742171085944</v>
+        <v>0.02614630002295603</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>32595.46967576235</v>
+        <v>32715.65201015491</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.04872736072626074</v>
+        <v>0.02637758141351989</v>
       </c>
     </row>
     <row r="20">
@@ -883,13 +883,13 @@
         <v>0.8338307808027936</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.01004915003566171</v>
+        <v>0.005150244084100804</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>27756.48257825524</v>
+        <v>16231.60938423313</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.01013892492766191</v>
+        <v>0.005160906312789811</v>
       </c>
     </row>
     <row r="21">
@@ -905,13 +905,13 @@
         <v>1.328144906436728</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.01889121296349402</v>
+        <v>0.006436103222776605</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>35534.2330256165</v>
+        <v>15932.23312695837</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.01878376528503781</v>
+        <v>0.00645058546766663</v>
       </c>
     </row>
     <row r="22">
@@ -921,19 +921,19 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>0.2263447316982285</v>
+        <v>0.2263447316982287</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1.131723658491142</v>
+        <v>1.131723658491144</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.02533804296830943</v>
+        <v>0.01172220648297925</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>40695.11838112678</v>
+        <v>25564.64710961189</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.02534699317900928</v>
+        <v>0.01196318220619112</v>
       </c>
     </row>
     <row r="23">
@@ -949,13 +949,13 @@
         <v>1.046212990167654</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.02454439132798581</v>
+        <v>0.01160505130302901</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>43460.58792427857</v>
+        <v>28129.60073153302</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.02437733635667043</v>
+        <v>0.0116354059288617</v>
       </c>
     </row>
     <row r="24">
@@ -971,13 +971,13 @@
         <v>0.8445994536332054</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.02608386901064053</v>
+        <v>0.007783634788307064</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>29141.94433738897</v>
+        <v>14007.705019922</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.02590862298367062</v>
+        <v>0.007885174307238885</v>
       </c>
     </row>
     <row r="25">
@@ -993,13 +993,13 @@
         <v>0.9870371232036546</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.00656253138839626</v>
+        <v>0.0004871740219642358</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>9739.054404133232</v>
+        <v>764.8014534853864</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.006597644843243317</v>
+        <v>0.0003868957886519034</v>
       </c>
     </row>
     <row r="26">
@@ -1015,13 +1015,13 @@
         <v>1.036858742910292</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.04290519077631972</v>
+        <v>0.01329391032751322</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>50666.49235914159</v>
+        <v>24589.90620727371</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.04280486563839878</v>
+        <v>0.01328720554330827</v>
       </c>
     </row>
     <row r="27">
@@ -1037,13 +1037,13 @@
         <v>0.7274616168526672</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.04542865511481419</v>
+        <v>0.02364430497448098</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>38131.90511435154</v>
+        <v>31959.05868003005</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.04534990822425392</v>
+        <v>0.02369274196412583</v>
       </c>
     </row>
     <row r="28">
@@ -1059,13 +1059,13 @@
         <v>1.088307630198285</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.1078401764613783</v>
+        <v>0.06047972069402941</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>38005.24719258782</v>
+        <v>50219.37436710298</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.1079074911641977</v>
+        <v>0.06062714430374739</v>
       </c>
     </row>
     <row r="29">
@@ -1081,13 +1081,13 @@
         <v>1.240703519294513</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.1328911995670021</v>
+        <v>0.07212177827632604</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>36811.41180888616</v>
+        <v>54421.06577074039</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.1329723749001658</v>
+        <v>0.07206784019601217</v>
       </c>
     </row>
     <row r="30">
@@ -1103,13 +1103,13 @@
         <v>1.094879126885175</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.1169538806985804</v>
+        <v>0.05418041849579801</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>45488.27862411248</v>
+        <v>52380.31109826872</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.1169394943013584</v>
+        <v>0.05448520360053895</v>
       </c>
     </row>
     <row r="31">
@@ -1125,13 +1125,13 @@
         <v>0.9045908504845974</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.05840869634115225</v>
+        <v>0.03060992857623725</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>30676.82280907984</v>
+        <v>36420.422437164</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.05845990332803951</v>
+        <v>0.0308495681025902</v>
       </c>
     </row>
     <row r="32">
@@ -1147,13 +1147,13 @@
         <v>1.231110211840753</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.04728352846993988</v>
+        <v>0.02066032657441137</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>39710.83293060772</v>
+        <v>33878.86671652133</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.04727173971505261</v>
+        <v>0.02074642874247436</v>
       </c>
     </row>
     <row r="33">
@@ -1169,13 +1169,13 @@
         <v>1.178065167630268</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.0213984486284778</v>
+        <v>0.01198548664889139</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>41865.67339496245</v>
+        <v>30632.96506520081</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.02132743767136852</v>
+        <v>0.01194849667919027</v>
       </c>
     </row>
     <row r="34">
@@ -1185,19 +1185,19 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.2249419876613653</v>
+        <v>0.2249419876613652</v>
       </c>
       <c r="C34" s="2" t="n">
         <v>1.124709938306826</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.02718386663399109</v>
+        <v>0.01509483778368569</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>44226.96255865344</v>
+        <v>34445.55043212837</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.02713366807875624</v>
+        <v>0.01515268057163923</v>
       </c>
     </row>
     <row r="35">
@@ -1213,13 +1213,13 @@
         <v>1.008768244313551</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.04372221156634065</v>
+        <v>0.02057526433370866</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>46311.51283437619</v>
+        <v>37420.25646184199</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.04334769423104392</v>
+        <v>0.02054896957197678</v>
       </c>
     </row>
     <row r="36">
@@ -1235,13 +1235,13 @@
         <v>1.174175849898935</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.00185833844612147</v>
+        <v>0.001751955494492962</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2223.439635714283</v>
+        <v>3374.752045739908</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.002023967935993562</v>
+        <v>0.001789601613690949</v>
       </c>
     </row>
     <row r="37">
@@ -1257,13 +1257,13 @@
         <v>1.166451240267723</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>-0.0004333285980325177</v>
+        <v>0.001903569810686068</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-307.7871420019073</v>
+        <v>3046.597343983129</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-0.0004251562942802745</v>
+        <v>0.002086140527671682</v>
       </c>
     </row>
   </sheetData>
@@ -1322,16 +1322,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.2390521776954898</v>
+        <v>0.2390521776954897</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1.195260888477449</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.008835497283213624</v>
+        <v>0.005180061838410116</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.01065608290109359</v>
+        <v>0.006437125898270101</v>
       </c>
     </row>
     <row r="3">
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.2274898096274938</v>
+        <v>0.2274898096274939</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>1.137449048137469</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.02141152274315095</v>
+        <v>0.01219201624900328</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.02417835258795758</v>
+        <v>0.01413813013355232</v>
       </c>
     </row>
     <row r="4">
@@ -1366,10 +1366,10 @@
         <v>1.059964102783094</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.03796827617847924</v>
+        <v>0.02077780688944944</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.03799510846530392</v>
+        <v>0.02116078798275892</v>
       </c>
     </row>
     <row r="5">
@@ -1385,10 +1385,10 @@
         <v>1.117533848642272</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.01630391269788673</v>
+        <v>0.009933490800290433</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.02067974948778655</v>
+        <v>0.01265153383679903</v>
       </c>
     </row>
   </sheetData>
